--- a/public/exports/55606617.xlsx
+++ b/public/exports/55606617.xlsx
@@ -331,16 +331,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090722</t>
+          <t xml:space="preserve">2091223</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F7">
-        <v>664</v>
+        <v>721</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -381,7 +381,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091223</t>
+          <t xml:space="preserve">226182</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -390,7 +390,7 @@
         </is>
       </c>
       <c r="F8">
-        <v>721</v>
+        <v>1836</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -431,16 +431,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159956</t>
+          <t xml:space="preserve">226183</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F9">
-        <v>1497</v>
+        <v>3484</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,16 +481,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028726</t>
+          <t xml:space="preserve">226183</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F10">
-        <v>546</v>
+        <v>3648</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -531,16 +531,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028726</t>
+          <t xml:space="preserve">228394, 228395, 228397, 228398, 228399, 228396</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F11">
-        <v>546</v>
+        <v>3996</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -581,16 +581,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028740</t>
+          <t xml:space="preserve">228812</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F12">
-        <v>345</v>
+        <v>1671</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -631,16 +631,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">7029060</t>
+          <t xml:space="preserve">228813</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F13">
-        <v>363</v>
+        <v>4660</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -681,16 +681,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">713681, 2080863</t>
+          <t xml:space="preserve">7028726</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F14">
-        <v>581</v>
+        <v>546</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -731,16 +731,16 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">713683, 2080863</t>
+          <t xml:space="preserve">7028726</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F15">
-        <v>308</v>
+        <v>546</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -781,16 +781,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">713690, 2080863</t>
+          <t xml:space="preserve">713681, 2080863</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F16">
-        <v>382</v>
+        <v>581</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -831,16 +831,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">8963405</t>
+          <t xml:space="preserve">713690, 2080863</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F17">
-        <v>1989</v>
+        <v>382</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -881,30 +881,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079383</t>
+          <t xml:space="preserve">8963405</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F18">
-        <v>595</v>
+        <v>1989</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054392</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-10-30</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -931,25 +931,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079383</t>
+          <t xml:space="preserve">2024338</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F19">
-        <v>743</v>
+        <v>650</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054393</t>
+          <t xml:space="preserve">200056021</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-10-30</t>
+          <t xml:space="preserve">2021-12-16</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F20">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F21">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F22">
@@ -1131,20 +1131,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024338</t>
+          <t xml:space="preserve">2024382</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F23">
-        <v>650</v>
+        <v>1522</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056021</t>
+          <t xml:space="preserve">200056022</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024382</t>
+          <t xml:space="preserve">8785521</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1190,11 +1190,11 @@
         </is>
       </c>
       <c r="F24">
-        <v>1522</v>
+        <v>4156</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056022</t>
+          <t xml:space="preserve">200055994</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">8785521</t>
+          <t xml:space="preserve">2090160</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1240,16 +1240,16 @@
         </is>
       </c>
       <c r="F25">
-        <v>4156</v>
+        <v>354</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055994</t>
+          <t xml:space="preserve">311076836</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-16</t>
+          <t xml:space="preserve">2024-10-03</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1281,35 +1281,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090160</t>
+          <t xml:space="preserve">713683, 2080863</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F26">
-        <v>354</v>
+        <v>308</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311076836</t>
+          <t xml:space="preserve">311231684</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-10-03</t>
+          <t xml:space="preserve">2027-03-02</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1331,25 +1331,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">228394, 228395, 228397, 228398, 228399, 228396</t>
+          <t xml:space="preserve">2159956</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F27">
-        <v>3996</v>
+        <v>1497</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311247295</t>
+          <t xml:space="preserve">311356616</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-15</t>
+          <t xml:space="preserve">2029-01-25</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1381,25 +1381,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079345</t>
+          <t xml:space="preserve">2079383</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F28">
-        <v>1324</v>
+        <v>595</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586007</t>
+          <t xml:space="preserve">311567481</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-07</t>
+          <t xml:space="preserve">2031-12-13</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1431,25 +1431,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079345</t>
+          <t xml:space="preserve">2079383</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F29">
-        <v>1320</v>
+        <v>743</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586007</t>
+          <t xml:space="preserve">311567481</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-07</t>
+          <t xml:space="preserve">2031-12-13</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1481,25 +1481,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079345</t>
+          <t xml:space="preserve">2159266</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F30">
-        <v>445</v>
+        <v>7598</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586007</t>
+          <t xml:space="preserve">311586010</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-07</t>
+          <t xml:space="preserve">2031-12-15</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1531,25 +1531,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079345</t>
+          <t xml:space="preserve">8785521</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F31">
-        <v>493</v>
+        <v>6125</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586007</t>
+          <t xml:space="preserve">311586012</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-07</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1581,25 +1581,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079345</t>
+          <t xml:space="preserve">8785521</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F32">
-        <v>1324</v>
+        <v>863</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586007</t>
+          <t xml:space="preserve">311586012</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-07</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1631,25 +1631,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079345</t>
+          <t xml:space="preserve">8785521</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F33">
-        <v>1018</v>
+        <v>861</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586007</t>
+          <t xml:space="preserve">311586012</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-07</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1681,25 +1681,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159169</t>
+          <t xml:space="preserve">8785521</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F34">
-        <v>537</v>
+        <v>958</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311585999</t>
+          <t xml:space="preserve">311586012</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-07</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1731,25 +1731,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091192</t>
+          <t xml:space="preserve">8785521</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F35">
-        <v>8026</v>
+        <v>858</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566793</t>
+          <t xml:space="preserve">311586012</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-08</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159266</t>
+          <t xml:space="preserve">1301761</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1790,16 +1790,16 @@
         </is>
       </c>
       <c r="F36">
-        <v>7598</v>
+        <v>894</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586010</t>
+          <t xml:space="preserve">311586014</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-15</t>
+          <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1831,25 +1831,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028740</t>
+          <t xml:space="preserve">1301761</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F37">
-        <v>1337</v>
+        <v>568</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588713</t>
+          <t xml:space="preserve">311586014</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-15</t>
+          <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1881,25 +1881,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">8785521</t>
+          <t xml:space="preserve">1301761</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F38">
-        <v>6125</v>
+        <v>493</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586012</t>
+          <t xml:space="preserve">311586014</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1931,25 +1931,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">8785521</t>
+          <t xml:space="preserve">1301761</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F39">
-        <v>863</v>
+        <v>449</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586012</t>
+          <t xml:space="preserve">311586014</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1981,25 +1981,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">8785521</t>
+          <t xml:space="preserve">1301761</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F40">
-        <v>861</v>
+        <v>445</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586012</t>
+          <t xml:space="preserve">311586014</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2031,25 +2031,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">8785521</t>
+          <t xml:space="preserve">1301761</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F41">
-        <v>958</v>
+        <v>798</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586012</t>
+          <t xml:space="preserve">311586014</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2081,25 +2081,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">8785521</t>
+          <t xml:space="preserve">1301761</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F42">
-        <v>858</v>
+        <v>798</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586012</t>
+          <t xml:space="preserve">311586014</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2131,25 +2131,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2160102</t>
+          <t xml:space="preserve">1301761</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F43">
-        <v>4371</v>
+        <v>772</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586013</t>
+          <t xml:space="preserve">311586014</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-11</t>
+          <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2181,25 +2181,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2160102</t>
+          <t xml:space="preserve">1301761</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F44">
-        <v>2187</v>
+        <v>884</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586013</t>
+          <t xml:space="preserve">311586014</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-11</t>
+          <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2231,25 +2231,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2160102</t>
+          <t xml:space="preserve">1301761</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F45">
-        <v>362</v>
+        <v>621</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586013</t>
+          <t xml:space="preserve">311586014</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-11</t>
+          <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2286,11 +2286,11 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F46">
-        <v>894</v>
+        <v>621</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2336,11 +2336,11 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F47">
-        <v>568</v>
+        <v>621</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2386,11 +2386,11 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F48">
-        <v>493</v>
+        <v>1214</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2431,25 +2431,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301761</t>
+          <t xml:space="preserve">7028726</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F49">
-        <v>449</v>
+        <v>326</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586014</t>
+          <t xml:space="preserve">311588891</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-17</t>
+          <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2481,25 +2481,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301761</t>
+          <t xml:space="preserve">7028726</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F50">
-        <v>445</v>
+        <v>1167</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586014</t>
+          <t xml:space="preserve">311588891</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-17</t>
+          <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2531,25 +2531,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301761</t>
+          <t xml:space="preserve">7028726</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F51">
-        <v>798</v>
+        <v>629</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586014</t>
+          <t xml:space="preserve">311588891</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-17</t>
+          <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2581,25 +2581,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301761</t>
+          <t xml:space="preserve">7028726</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F52">
-        <v>798</v>
+        <v>785</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586014</t>
+          <t xml:space="preserve">311588891</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-17</t>
+          <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2631,25 +2631,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301761</t>
+          <t xml:space="preserve">7028726</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F53">
-        <v>772</v>
+        <v>629</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586014</t>
+          <t xml:space="preserve">311588891</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-17</t>
+          <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2681,25 +2681,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301761</t>
+          <t xml:space="preserve">7028726</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F54">
-        <v>884</v>
+        <v>1151</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586014</t>
+          <t xml:space="preserve">311588891</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-17</t>
+          <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2731,25 +2731,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301761</t>
+          <t xml:space="preserve">7028726</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F55">
-        <v>621</v>
+        <v>571</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586014</t>
+          <t xml:space="preserve">311588891</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-17</t>
+          <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2781,25 +2781,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301761</t>
+          <t xml:space="preserve">2079333</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F56">
-        <v>621</v>
+        <v>2799</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586014</t>
+          <t xml:space="preserve">311590065</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-17</t>
+          <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2831,25 +2831,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301761</t>
+          <t xml:space="preserve">2079333</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F57">
-        <v>621</v>
+        <v>1487</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586014</t>
+          <t xml:space="preserve">311590063</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-17</t>
+          <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2881,25 +2881,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301761</t>
+          <t xml:space="preserve">2157348</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F58">
-        <v>1214</v>
+        <v>262</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586014</t>
+          <t xml:space="preserve">311590033</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-17</t>
+          <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090722</t>
+          <t xml:space="preserve">2159280</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2940,16 +2940,16 @@
         </is>
       </c>
       <c r="F59">
-        <v>3240</v>
+        <v>5757</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588726</t>
+          <t xml:space="preserve">311589965</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2981,25 +2981,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090722</t>
+          <t xml:space="preserve">2079333</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F60">
-        <v>554</v>
+        <v>904</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588726</t>
+          <t xml:space="preserve">311598300</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2032-05-06</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3031,25 +3031,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090722</t>
+          <t xml:space="preserve">2079333</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F61">
-        <v>1528</v>
+        <v>839</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588726</t>
+          <t xml:space="preserve">311601624</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2032-05-19</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3081,25 +3081,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090722</t>
+          <t xml:space="preserve">2079333</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F62">
-        <v>2017</v>
+        <v>863</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588726</t>
+          <t xml:space="preserve">311601624</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2032-05-19</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3131,25 +3131,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090722</t>
+          <t xml:space="preserve">1301761</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F63">
-        <v>1008</v>
+        <v>402</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588726</t>
+          <t xml:space="preserve">311622362</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3181,25 +3181,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090722</t>
+          <t xml:space="preserve">2091208</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F64">
-        <v>900</v>
+        <v>2623</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588726</t>
+          <t xml:space="preserve">311622363</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159169</t>
+          <t xml:space="preserve">2091211</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3240,16 +3240,16 @@
         </is>
       </c>
       <c r="F65">
-        <v>5857</v>
+        <v>1472</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588721</t>
+          <t xml:space="preserve">311622365</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3281,25 +3281,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159169</t>
+          <t xml:space="preserve">2159279</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F66">
-        <v>969</v>
+        <v>1712</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588722</t>
+          <t xml:space="preserve">311622355</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028740</t>
+          <t xml:space="preserve">2159316</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3340,16 +3340,16 @@
         </is>
       </c>
       <c r="F67">
-        <v>1703</v>
+        <v>356</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588729</t>
+          <t xml:space="preserve">311622352</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3381,25 +3381,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028740</t>
+          <t xml:space="preserve">8785521</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F68">
-        <v>663</v>
+        <v>4389</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588729</t>
+          <t xml:space="preserve">311622359</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3431,25 +3431,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028740</t>
+          <t xml:space="preserve">2090160</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F69">
-        <v>273</v>
+        <v>2533</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588729</t>
+          <t xml:space="preserve">311623162</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2032-08-25</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028740</t>
+          <t xml:space="preserve">2091192</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F70">
-        <v>1925</v>
+        <v>8026</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588729</t>
+          <t xml:space="preserve">311653142</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2033-01-10</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3531,25 +3531,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028740</t>
+          <t xml:space="preserve">2023800</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F71">
-        <v>1256</v>
+        <v>1662</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588729</t>
+          <t xml:space="preserve">311669678</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3581,25 +3581,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028726</t>
+          <t xml:space="preserve">2023800</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F72">
-        <v>326</v>
+        <v>2375</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588891</t>
+          <t xml:space="preserve">311669678</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-29</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3631,25 +3631,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028726</t>
+          <t xml:space="preserve">2023800</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F73">
-        <v>1167</v>
+        <v>1847</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588891</t>
+          <t xml:space="preserve">311669678</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-29</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028726</t>
+          <t xml:space="preserve">2023800</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3690,16 +3690,16 @@
         </is>
       </c>
       <c r="F74">
-        <v>629</v>
+        <v>1226</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588891</t>
+          <t xml:space="preserve">311669678</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-29</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028726</t>
+          <t xml:space="preserve">2023800</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3740,16 +3740,16 @@
         </is>
       </c>
       <c r="F75">
-        <v>785</v>
+        <v>1301</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588891</t>
+          <t xml:space="preserve">311669678</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-29</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028726</t>
+          <t xml:space="preserve">2023800</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3790,16 +3790,16 @@
         </is>
       </c>
       <c r="F76">
-        <v>629</v>
+        <v>2569</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588891</t>
+          <t xml:space="preserve">311669678</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-29</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028726</t>
+          <t xml:space="preserve">2023800</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3840,16 +3840,16 @@
         </is>
       </c>
       <c r="F77">
-        <v>1151</v>
+        <v>606</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588891</t>
+          <t xml:space="preserve">311669678</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-29</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3881,25 +3881,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028726</t>
+          <t xml:space="preserve">2023800</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F78">
-        <v>571</v>
+        <v>323</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588891</t>
+          <t xml:space="preserve">311669678</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-29</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3931,25 +3931,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079333</t>
+          <t xml:space="preserve">2079345</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F79">
-        <v>2799</v>
+        <v>1324</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590065</t>
+          <t xml:space="preserve">311669680</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-01</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3981,25 +3981,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079333</t>
+          <t xml:space="preserve">2079345</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F80">
-        <v>1487</v>
+        <v>1320</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590063</t>
+          <t xml:space="preserve">311669680</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-01</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4036,20 +4036,20 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F81">
-        <v>2387</v>
+        <v>445</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590061</t>
+          <t xml:space="preserve">311669680</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-01</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4086,20 +4086,20 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F82">
-        <v>787</v>
+        <v>2387</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590058</t>
+          <t xml:space="preserve">311669680</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-01</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4131,25 +4131,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2157348</t>
+          <t xml:space="preserve">2079345</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F83">
-        <v>262</v>
+        <v>493</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590033</t>
+          <t xml:space="preserve">311669680</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-01</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4181,25 +4181,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159280</t>
+          <t xml:space="preserve">2079345</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F84">
-        <v>5757</v>
+        <v>787</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311589965</t>
+          <t xml:space="preserve">311669680</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-01</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4231,25 +4231,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025107</t>
+          <t xml:space="preserve">2079345</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F85">
-        <v>2141</v>
+        <v>1324</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590424</t>
+          <t xml:space="preserve">311669680</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-04</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4281,25 +4281,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025107</t>
+          <t xml:space="preserve">2079345</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F86">
-        <v>1272</v>
+        <v>1018</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590424</t>
+          <t xml:space="preserve">311669680</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-04</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4331,25 +4331,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025107</t>
+          <t xml:space="preserve">2090722</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F87">
-        <v>4563</v>
+        <v>3240</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590424</t>
+          <t xml:space="preserve">311669679</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-04</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4381,25 +4381,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079333</t>
+          <t xml:space="preserve">2090722</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F88">
-        <v>904</v>
+        <v>554</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598300</t>
+          <t xml:space="preserve">311669679</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-06</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4431,25 +4431,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079333</t>
+          <t xml:space="preserve">2090722</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F89">
-        <v>839</v>
+        <v>1528</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601624</t>
+          <t xml:space="preserve">311669679</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-19</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4481,25 +4481,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079333</t>
+          <t xml:space="preserve">2090722</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F90">
-        <v>863</v>
+        <v>2017</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601624</t>
+          <t xml:space="preserve">311669679</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-19</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4531,25 +4531,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2160102</t>
+          <t xml:space="preserve">2090722</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F91">
-        <v>468</v>
+        <v>1008</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601932</t>
+          <t xml:space="preserve">311669679</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-20</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4581,25 +4581,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301761</t>
+          <t xml:space="preserve">2090722</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F92">
-        <v>402</v>
+        <v>664</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622362</t>
+          <t xml:space="preserve">311669679</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-23</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4631,25 +4631,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091208</t>
+          <t xml:space="preserve">2090722</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F93">
-        <v>2623</v>
+        <v>900</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622363</t>
+          <t xml:space="preserve">311669679</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-23</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091211</t>
+          <t xml:space="preserve">7165564</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4690,16 +4690,16 @@
         </is>
       </c>
       <c r="F94">
-        <v>1472</v>
+        <v>1345</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622365</t>
+          <t xml:space="preserve">311669671</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-23</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4731,25 +4731,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159279</t>
+          <t xml:space="preserve">7165564</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F95">
-        <v>1712</v>
+        <v>6142</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622355</t>
+          <t xml:space="preserve">311669668</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-23</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4781,25 +4781,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159316</t>
+          <t xml:space="preserve">7165564</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F96">
-        <v>356</v>
+        <v>3329</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622352</t>
+          <t xml:space="preserve">311669668</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-23</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4831,25 +4831,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2160102</t>
+          <t xml:space="preserve">8785521</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F97">
-        <v>3349</v>
+        <v>6161</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622381</t>
+          <t xml:space="preserve">311669688</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-23</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4881,25 +4881,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">7029060</t>
+          <t xml:space="preserve">2025107</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F98">
-        <v>398</v>
+        <v>2141</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622350</t>
+          <t xml:space="preserve">311670133</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-23</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4931,25 +4931,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">8785521</t>
+          <t xml:space="preserve">2025107</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F99">
-        <v>4389</v>
+        <v>263</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622359</t>
+          <t xml:space="preserve">311670133</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-23</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090160</t>
+          <t xml:space="preserve">2025107</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4990,16 +4990,16 @@
         </is>
       </c>
       <c r="F100">
-        <v>2533</v>
+        <v>1272</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311623162</t>
+          <t xml:space="preserve">311670133</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-25</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5031,25 +5031,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023800</t>
+          <t xml:space="preserve">2025107</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F101">
-        <v>1662</v>
+        <v>4563</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311641604</t>
+          <t xml:space="preserve">311670133</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-09</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5081,25 +5081,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023800</t>
+          <t xml:space="preserve">2159169</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F102">
-        <v>323</v>
+        <v>5857</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311641603</t>
+          <t xml:space="preserve">311670404</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-09</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5131,25 +5131,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023800</t>
+          <t xml:space="preserve">2159169</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F103">
-        <v>2375</v>
+        <v>969</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644178</t>
+          <t xml:space="preserve">311670404</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-22</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5181,25 +5181,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023800</t>
+          <t xml:space="preserve">2159169</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F104">
-        <v>1847</v>
+        <v>537</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644178</t>
+          <t xml:space="preserve">311670404</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-22</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5231,25 +5231,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023800</t>
+          <t xml:space="preserve">7029060</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F105">
-        <v>1226</v>
+        <v>363</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644178</t>
+          <t xml:space="preserve">311670169</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-22</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5281,25 +5281,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023800</t>
+          <t xml:space="preserve">7029060</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F106">
-        <v>1301</v>
+        <v>398</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644178</t>
+          <t xml:space="preserve">311670169</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-22</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5331,25 +5331,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023800</t>
+          <t xml:space="preserve">7706803</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F107">
-        <v>2569</v>
+        <v>1559</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644178</t>
+          <t xml:space="preserve">311670403</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-22</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5381,25 +5381,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023800</t>
+          <t xml:space="preserve">2091204</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F108">
-        <v>606</v>
+        <v>1130</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644178</t>
+          <t xml:space="preserve">311674024</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-22</t>
+          <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5431,25 +5431,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091170</t>
+          <t xml:space="preserve">2091204</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F109">
-        <v>1000</v>
+        <v>1050</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669683</t>
+          <t xml:space="preserve">311674024</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-28</t>
+          <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5481,25 +5481,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091170</t>
+          <t xml:space="preserve">2091204</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F110">
-        <v>1611</v>
+        <v>865</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669683</t>
+          <t xml:space="preserve">311674026</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-28</t>
+          <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5531,25 +5531,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091170</t>
+          <t xml:space="preserve">2091204</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F111">
-        <v>580</v>
+        <v>283</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669684</t>
+          <t xml:space="preserve">311674024</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-28</t>
+          <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091170</t>
+          <t xml:space="preserve">9494877</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -5590,16 +5590,16 @@
         </is>
       </c>
       <c r="F112">
-        <v>1223</v>
+        <v>365</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669685</t>
+          <t xml:space="preserve">311707954</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-28</t>
+          <t xml:space="preserve">2033-09-15</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">226182</t>
+          <t xml:space="preserve">2023609</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -5640,16 +5640,16 @@
         </is>
       </c>
       <c r="F113">
-        <v>1836</v>
+        <v>1289</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669673</t>
+          <t xml:space="preserve">311716225</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-28</t>
+          <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5681,25 +5681,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">226183</t>
+          <t xml:space="preserve">2077515</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F114">
-        <v>3484</v>
+        <v>685</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669673</t>
+          <t xml:space="preserve">311716223</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-28</t>
+          <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5731,25 +5731,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">226183</t>
+          <t xml:space="preserve">2077515</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F115">
-        <v>3648</v>
+        <v>685</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669673</t>
+          <t xml:space="preserve">311716224</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-28</t>
+          <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">7165564</t>
+          <t xml:space="preserve">2079445</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -5790,16 +5790,16 @@
         </is>
       </c>
       <c r="F116">
-        <v>1345</v>
+        <v>616</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669671</t>
+          <t xml:space="preserve">311716226</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-28</t>
+          <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5831,25 +5831,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">7165564</t>
+          <t xml:space="preserve">2157348</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F117">
-        <v>6142</v>
+        <v>284</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669668</t>
+          <t xml:space="preserve">311716216</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-28</t>
+          <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5881,25 +5881,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">7165564</t>
+          <t xml:space="preserve">2157348</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F118">
-        <v>3329</v>
+        <v>680</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669668</t>
+          <t xml:space="preserve">311716215</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-28</t>
+          <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5931,25 +5931,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">8785521</t>
+          <t xml:space="preserve">2159279</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F119">
-        <v>6161</v>
+        <v>351</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669688</t>
+          <t xml:space="preserve">311716218</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-28</t>
+          <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5981,25 +5981,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">100191021</t>
+          <t xml:space="preserve">2159279</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F120">
-        <v>569</v>
+        <v>1201</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670402</t>
+          <t xml:space="preserve">311716217</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-29</t>
+          <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6031,25 +6031,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025107</t>
+          <t xml:space="preserve">2159956</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F121">
-        <v>263</v>
+        <v>608</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670166</t>
+          <t xml:space="preserve">311716211</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-29</t>
+          <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6081,25 +6081,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">228812</t>
+          <t xml:space="preserve">2159956</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F122">
-        <v>1671</v>
+        <v>619</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670400</t>
+          <t xml:space="preserve">311716210</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-29</t>
+          <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -6131,25 +6131,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">228813</t>
+          <t xml:space="preserve">2159956</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F123">
-        <v>4660</v>
+        <v>619</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670401</t>
+          <t xml:space="preserve">311716212</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-29</t>
+          <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">7706803</t>
+          <t xml:space="preserve">2160430</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -6190,16 +6190,16 @@
         </is>
       </c>
       <c r="F124">
-        <v>1559</v>
+        <v>589</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670403</t>
+          <t xml:space="preserve">311716227</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-29</t>
+          <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6231,25 +6231,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091204</t>
+          <t xml:space="preserve">8490054</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F125">
-        <v>1130</v>
+        <v>366</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674024</t>
+          <t xml:space="preserve">311716208</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-17</t>
+          <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6281,25 +6281,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091204</t>
+          <t xml:space="preserve">9889329</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="F126">
-        <v>1050</v>
+        <v>335</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674024</t>
+          <t xml:space="preserve">311716228</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-17</t>
+          <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6331,25 +6331,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091204</t>
+          <t xml:space="preserve">9889332</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F127">
-        <v>865</v>
+        <v>423</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674026</t>
+          <t xml:space="preserve">311716230</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-17</t>
+          <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6381,25 +6381,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091204</t>
+          <t xml:space="preserve">9889334</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F128">
-        <v>283</v>
+        <v>423</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674024</t>
+          <t xml:space="preserve">311716229</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-17</t>
+          <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6431,25 +6431,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">9494877</t>
+          <t xml:space="preserve">9889335</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">59</t>
         </is>
       </c>
       <c r="F129">
-        <v>365</v>
+        <v>687</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311707954</t>
+          <t xml:space="preserve">311716220</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-15</t>
+          <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6481,20 +6481,20 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023609</t>
+          <t xml:space="preserve">9889336</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="F130">
-        <v>1289</v>
+        <v>1253</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716225</t>
+          <t xml:space="preserve">311716222</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6531,25 +6531,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2077515</t>
+          <t xml:space="preserve">8490055</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F131">
-        <v>685</v>
+        <v>736</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716223</t>
+          <t xml:space="preserve">311723773</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-19</t>
+          <t xml:space="preserve">2033-11-21</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6581,25 +6581,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2077515</t>
+          <t xml:space="preserve">2079621</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F132">
-        <v>685</v>
+        <v>916</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716224</t>
+          <t xml:space="preserve">311726046</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-19</t>
+          <t xml:space="preserve">2033-11-30</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6631,25 +6631,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079445</t>
+          <t xml:space="preserve">100191021</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F133">
-        <v>616</v>
+        <v>569</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716226</t>
+          <t xml:space="preserve">311740622</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-19</t>
+          <t xml:space="preserve">2034-02-22</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6681,25 +6681,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2157348</t>
+          <t xml:space="preserve">2157286</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F134">
-        <v>284</v>
+        <v>563</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716216</t>
+          <t xml:space="preserve">311740693</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-19</t>
+          <t xml:space="preserve">2034-02-23</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6726,30 +6726,30 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">167</t>
+          <t xml:space="preserve">740</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2157348</t>
+          <t xml:space="preserve">1461683</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F135">
-        <v>680</v>
+        <v>863</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716215</t>
+          <t xml:space="preserve">311814921</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-19</t>
+          <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6781,25 +6781,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159279</t>
+          <t xml:space="preserve">2025808</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F136">
-        <v>351</v>
+        <v>781</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716218</t>
+          <t xml:space="preserve">311814922</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-19</t>
+          <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6831,25 +6831,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159279</t>
+          <t xml:space="preserve">2025808</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F137">
-        <v>1201</v>
+        <v>856</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716217</t>
+          <t xml:space="preserve">311814922</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-19</t>
+          <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159956</t>
+          <t xml:space="preserve">2025855</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -6890,16 +6890,16 @@
         </is>
       </c>
       <c r="F138">
-        <v>608</v>
+        <v>361</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716211</t>
+          <t xml:space="preserve">311814917</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-19</t>
+          <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6931,25 +6931,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159956</t>
+          <t xml:space="preserve">7028595</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F139">
-        <v>619</v>
+        <v>416</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716210</t>
+          <t xml:space="preserve">311814918</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-19</t>
+          <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6981,25 +6981,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159956</t>
+          <t xml:space="preserve">7028726</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F140">
-        <v>619</v>
+        <v>430</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716212</t>
+          <t xml:space="preserve">311814920</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-19</t>
+          <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7031,25 +7031,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2160430</t>
+          <t xml:space="preserve">7028766</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F141">
-        <v>589</v>
+        <v>458</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716227</t>
+          <t xml:space="preserve">311814924</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-19</t>
+          <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -7081,25 +7081,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">8490054</t>
+          <t xml:space="preserve">8101016</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F142">
-        <v>366</v>
+        <v>938</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716208</t>
+          <t xml:space="preserve">311814900</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-19</t>
+          <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7131,25 +7131,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">9889329</t>
+          <t xml:space="preserve">9597370</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">70</t>
         </is>
       </c>
       <c r="F143">
-        <v>335</v>
+        <v>633</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716228</t>
+          <t xml:space="preserve">311814928</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-19</t>
+          <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7181,25 +7181,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">9889332</t>
+          <t xml:space="preserve">9807242</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F144">
-        <v>423</v>
+        <v>1483</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716230</t>
+          <t xml:space="preserve">311814923</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-19</t>
+          <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7226,30 +7226,30 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">167</t>
+          <t xml:space="preserve">706</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">9889334</t>
+          <t xml:space="preserve">4166473</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F145">
-        <v>423</v>
+        <v>1058</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716229</t>
+          <t xml:space="preserve">311816487</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-19</t>
+          <t xml:space="preserve">2035-03-10</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -7281,25 +7281,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">9889335</t>
+          <t xml:space="preserve">1300623</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">59</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F146">
-        <v>687</v>
+        <v>660</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716220</t>
+          <t xml:space="preserve">311821770</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-19</t>
+          <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7331,25 +7331,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">9889336</t>
+          <t xml:space="preserve">2023815</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F147">
-        <v>1253</v>
+        <v>320</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716222</t>
+          <t xml:space="preserve">311821767</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-19</t>
+          <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -7381,25 +7381,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">8490055</t>
+          <t xml:space="preserve">2024782</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F148">
-        <v>736</v>
+        <v>276</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723773</t>
+          <t xml:space="preserve">311821760</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-21</t>
+          <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079621</t>
+          <t xml:space="preserve">2025821</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -7440,16 +7440,16 @@
         </is>
       </c>
       <c r="F149">
-        <v>916</v>
+        <v>384</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726046</t>
+          <t xml:space="preserve">311821758</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-30</t>
+          <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2157286</t>
+          <t xml:space="preserve">2081592</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -7490,16 +7490,16 @@
         </is>
       </c>
       <c r="F150">
-        <v>563</v>
+        <v>303</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311740693</t>
+          <t xml:space="preserve">311821754</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-23</t>
+          <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7526,30 +7526,30 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">740</t>
+          <t xml:space="preserve">167</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">1461683</t>
+          <t xml:space="preserve">7165564</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F151">
-        <v>863</v>
+        <v>6412</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814921</t>
+          <t xml:space="preserve">311821755</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-03</t>
+          <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7581,25 +7581,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025808</t>
+          <t xml:space="preserve">9590756</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F152">
-        <v>781</v>
+        <v>498</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814922</t>
+          <t xml:space="preserve">311821766</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-03</t>
+          <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -7631,25 +7631,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025808</t>
+          <t xml:space="preserve">9889326</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F153">
-        <v>856</v>
+        <v>445</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814922</t>
+          <t xml:space="preserve">311821765</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-03</t>
+          <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -7681,25 +7681,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025855</t>
+          <t xml:space="preserve">9889328</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F154">
-        <v>361</v>
+        <v>925</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814917</t>
+          <t xml:space="preserve">311821763</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-03</t>
+          <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028595</t>
+          <t xml:space="preserve">2025114</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -7740,16 +7740,16 @@
         </is>
       </c>
       <c r="F155">
-        <v>416</v>
+        <v>319</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814918</t>
+          <t xml:space="preserve">311897780</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-03</t>
+          <t xml:space="preserve">2036-04-29</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -7781,25 +7781,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028726</t>
+          <t xml:space="preserve">2025114</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F156">
-        <v>430</v>
+        <v>1189</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814920</t>
+          <t xml:space="preserve">311897779</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-03</t>
+          <t xml:space="preserve">2036-04-29</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7831,25 +7831,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028766</t>
+          <t xml:space="preserve">2160102</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F157">
-        <v>458</v>
+        <v>4371</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814924</t>
+          <t xml:space="preserve">311897781</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-03</t>
+          <t xml:space="preserve">2036-04-29</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -7881,25 +7881,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">8101016</t>
+          <t xml:space="preserve">2160102</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F158">
-        <v>938</v>
+        <v>2187</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814900</t>
+          <t xml:space="preserve">311897781</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-03</t>
+          <t xml:space="preserve">2036-04-29</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -7931,25 +7931,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">9597370</t>
+          <t xml:space="preserve">2160102</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">70</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F159">
-        <v>633</v>
+        <v>3349</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814928</t>
+          <t xml:space="preserve">311897781</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-03</t>
+          <t xml:space="preserve">2036-04-29</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -7981,25 +7981,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">9807242</t>
+          <t xml:space="preserve">2160102</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F160">
-        <v>1483</v>
+        <v>362</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814923</t>
+          <t xml:space="preserve">311897781</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-03</t>
+          <t xml:space="preserve">2036-04-29</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -8026,30 +8026,30 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">706</t>
+          <t xml:space="preserve">167</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">4166473</t>
+          <t xml:space="preserve">2160102</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F161">
-        <v>1058</v>
+        <v>468</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311816487</t>
+          <t xml:space="preserve">311897781</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-10</t>
+          <t xml:space="preserve">2036-04-29</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300623</t>
+          <t xml:space="preserve">2081511</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -8090,16 +8090,16 @@
         </is>
       </c>
       <c r="F162">
-        <v>660</v>
+        <v>721</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821770</t>
+          <t xml:space="preserve">311903567</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-01</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023815</t>
+          <t xml:space="preserve">2091170</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -8140,16 +8140,16 @@
         </is>
       </c>
       <c r="F163">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821767</t>
+          <t xml:space="preserve">311903573</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-01</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -8181,25 +8181,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024782</t>
+          <t xml:space="preserve">2091170</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F164">
-        <v>276</v>
+        <v>1611</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821760</t>
+          <t xml:space="preserve">311903573</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-01</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8231,25 +8231,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025821</t>
+          <t xml:space="preserve">2091170</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F165">
-        <v>384</v>
+        <v>580</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821758</t>
+          <t xml:space="preserve">311903573</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-01</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8281,25 +8281,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2081592</t>
+          <t xml:space="preserve">2091170</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F166">
-        <v>303</v>
+        <v>1223</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821754</t>
+          <t xml:space="preserve">311903573</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-01</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -8331,25 +8331,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">7165564</t>
+          <t xml:space="preserve">7028726</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F167">
-        <v>6412</v>
+        <v>324</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821755</t>
+          <t xml:space="preserve">311903569</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-01</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -8381,25 +8381,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">9590756</t>
+          <t xml:space="preserve">7028740</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F168">
-        <v>498</v>
+        <v>1703</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821766</t>
+          <t xml:space="preserve">311903570</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-01</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -8431,25 +8431,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">9889326</t>
+          <t xml:space="preserve">7028740</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F169">
-        <v>445</v>
+        <v>345</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821765</t>
+          <t xml:space="preserve">311903570</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-01</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -8481,25 +8481,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">9889328</t>
+          <t xml:space="preserve">7028740</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F170">
-        <v>925</v>
+        <v>1337</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821763</t>
+          <t xml:space="preserve">311903570</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-01</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -8531,25 +8531,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025114</t>
+          <t xml:space="preserve">7028740</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F171">
-        <v>319</v>
+        <v>663</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897780</t>
+          <t xml:space="preserve">311903570</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-29</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -8581,25 +8581,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025114</t>
+          <t xml:space="preserve">7028740</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F172">
-        <v>1189</v>
+        <v>273</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897779</t>
+          <t xml:space="preserve">311903570</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-29</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8631,20 +8631,20 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2081511</t>
+          <t xml:space="preserve">7028740</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F173">
-        <v>721</v>
+        <v>1925</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903567</t>
+          <t xml:space="preserve">311903570</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -8681,20 +8681,20 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028726</t>
+          <t xml:space="preserve">7028740</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F174">
-        <v>324</v>
+        <v>1256</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903569</t>
+          <t xml:space="preserve">311903570</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">

--- a/public/exports/55606617.xlsx
+++ b/public/exports/55606617.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J174"/>
+  <dimension ref="A1:L174"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -29,35 +29,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Adresse</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postnr.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -81,33 +91,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Byvej 72</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">100822249</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>1058</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -131,33 +151,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Byvej 58</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">100822249</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">30</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>319</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -181,33 +211,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Byvej 72</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">100822249</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">32</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>427</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -231,33 +271,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Catherine Boothsvej 20</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">100854515</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>1283</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -281,33 +331,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Idrætsvej 65A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">2079625</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>342</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -331,33 +391,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Høvedstensvej 45C</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">2091223</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>721</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -381,33 +451,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Karise Alle 29</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">226182</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>1836</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -431,33 +511,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Karise Alle 31</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t xml:space="preserve">226183</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>3484</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,33 +571,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Krogstens Alle 51</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t xml:space="preserve">226183</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>3648</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -531,33 +631,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovrevej 432</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">228394, 228395, 228397, 228398, 228399, 228396</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>3996</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -581,33 +691,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tavlekærsvej 166</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t xml:space="preserve">228812</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>1671</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -631,33 +751,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tavlekærsvej 164</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t xml:space="preserve">228813</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>4660</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -681,33 +811,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovrevej 361A</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t xml:space="preserve">7028726</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>546</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -731,33 +871,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovrevej 361C</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t xml:space="preserve">7028726</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
         </is>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>546</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -781,33 +931,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Strandhavevej 218</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t xml:space="preserve">713681, 2080863</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>581</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -831,33 +991,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Strandhavevej 59</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t xml:space="preserve">713690, 2080863</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>382</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -881,33 +1051,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Avedøre Slettevej 7C</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t xml:space="preserve">8963405</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>1989</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -931,33 +1111,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovregade 41A</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024338</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>650</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve">200056021</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-12-16</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -981,33 +1171,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovregade 41C</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024338</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>650</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve">200056021</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-12-16</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1031,33 +1231,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovregade 41E</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024338</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>650</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">200056021</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-12-16</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1081,33 +1291,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovregade 41G</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024338</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>650</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">200056021</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-12-16</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1131,33 +1351,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovregade 41K</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024382</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>1522</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve">200056022</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-12-16</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1181,33 +1411,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovrevej 446</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t xml:space="preserve">8785521</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>4156</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">200055994</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-12-16</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1231,33 +1471,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovrevej 241</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2090160</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>354</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve">311076836</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t xml:space="preserve">2024-10-03</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1281,33 +1531,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovre Strandvej 31H</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t xml:space="preserve">713683, 2080863</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>308</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t xml:space="preserve">311231684</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-03-02</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1331,33 +1591,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Byvej 248D</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t xml:space="preserve">2159956</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
         </is>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>1497</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t xml:space="preserve">311356616</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-01-25</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1381,33 +1651,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Catherine Boothsvej 22</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t xml:space="preserve">2079383</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>595</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t xml:space="preserve">311567481</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-12-13</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1431,33 +1711,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Catherine Boothsvej 24A</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2079383</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>743</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t xml:space="preserve">311567481</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-12-13</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1481,33 +1771,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bødkerporten 1Y</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2159266</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>7598</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t xml:space="preserve">311586010</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-12-15</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1531,33 +1831,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovrevej 440A</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t xml:space="preserve">8785521</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>6125</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t xml:space="preserve">311586012</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1581,33 +1891,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovrevej 440</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t xml:space="preserve">8785521</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F32">
+      <c r="H32">
         <v>863</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t xml:space="preserve">311586012</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1631,33 +1951,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovrevej 440</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t xml:space="preserve">8785521</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>861</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t xml:space="preserve">311586012</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1681,33 +2011,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovrevej 440</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t xml:space="preserve">8785521</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>958</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t xml:space="preserve">311586012</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1731,33 +2071,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovrevej 440</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t xml:space="preserve">8785521</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F35">
+      <c r="H35">
         <v>858</v>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t xml:space="preserve">311586012</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1781,33 +2131,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t xml:space="preserve">1301761</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>894</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t xml:space="preserve">311586014</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1831,33 +2191,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t xml:space="preserve">1301761</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>568</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve">311586014</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1881,33 +2251,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t xml:space="preserve">1301761</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>493</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t xml:space="preserve">311586014</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1931,33 +2311,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t xml:space="preserve">1301761</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>449</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t xml:space="preserve">311586014</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1981,33 +2371,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t xml:space="preserve">1301761</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>445</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t xml:space="preserve">311586014</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2031,33 +2431,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t xml:space="preserve">1301761</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F41">
+      <c r="H41">
         <v>798</v>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t xml:space="preserve">311586014</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2081,33 +2491,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t xml:space="preserve">1301761</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>798</v>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t xml:space="preserve">311586014</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2131,33 +2551,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t xml:space="preserve">1301761</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>772</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t xml:space="preserve">311586014</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2181,33 +2611,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t xml:space="preserve">1301761</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>884</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t xml:space="preserve">311586014</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2231,33 +2671,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t xml:space="preserve">1301761</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F45">
+      <c r="H45">
         <v>621</v>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t xml:space="preserve">311586014</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2281,33 +2731,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t xml:space="preserve">1301761</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F46">
+      <c r="H46">
         <v>621</v>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t xml:space="preserve">311586014</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2331,33 +2791,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t xml:space="preserve">1301761</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F47">
+      <c r="H47">
         <v>621</v>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t xml:space="preserve">311586014</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2381,33 +2851,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t xml:space="preserve">1301761</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>1214</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t xml:space="preserve">311586014</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2431,33 +2911,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t xml:space="preserve">7028726</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F49">
+      <c r="H49">
         <v>326</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t xml:space="preserve">311588891</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2481,33 +2971,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t xml:space="preserve">7028726</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>1167</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t xml:space="preserve">311588891</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2531,33 +3031,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t xml:space="preserve">7028726</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F51">
+      <c r="H51">
         <v>629</v>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t xml:space="preserve">311588891</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2581,33 +3091,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t xml:space="preserve">7028726</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F52">
+      <c r="H52">
         <v>785</v>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t xml:space="preserve">311588891</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2631,33 +3151,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t xml:space="preserve">7028726</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F53">
+      <c r="H53">
         <v>629</v>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t xml:space="preserve">311588891</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2681,33 +3211,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t xml:space="preserve">7028726</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F54">
+      <c r="H54">
         <v>1151</v>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t xml:space="preserve">311588891</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2731,33 +3271,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t xml:space="preserve">7028726</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F55">
+      <c r="H55">
         <v>571</v>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t xml:space="preserve">311588891</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2781,33 +3331,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sollentuna Alle 1</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2079333</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F56">
+      <c r="H56">
         <v>2799</v>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t xml:space="preserve">311590065</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2831,33 +3391,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sollentuna Alle 1</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2079333</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F57">
+      <c r="H57">
         <v>1487</v>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t xml:space="preserve">311590063</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2881,33 +3451,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Byvej 78</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2157348</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F58">
+      <c r="H58">
         <v>262</v>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t xml:space="preserve">311590033</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2931,33 +3511,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Trædrejerporten 1A</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2159280</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F59">
+      <c r="H59">
         <v>5757</v>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t xml:space="preserve">311589965</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2981,33 +3571,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sollentuna Alle 1</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2079333</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F60">
+      <c r="H60">
         <v>904</v>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t xml:space="preserve">311598300</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-05-06</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3031,33 +3631,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sollentuna Alle 1</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2079333</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F61">
+      <c r="H61">
         <v>839</v>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t xml:space="preserve">311601624</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-05-19</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3081,33 +3691,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sollentuna Alle 1</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2079333</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F62">
+      <c r="H62">
         <v>863</v>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t xml:space="preserve">311601624</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-05-19</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3131,33 +3751,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t xml:space="preserve">1301761</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="F63">
+      <c r="H63">
         <v>402</v>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t xml:space="preserve">311622362</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3181,33 +3811,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovrevej 272</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2091208</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F64">
+      <c r="H64">
         <v>2623</v>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t xml:space="preserve">311622363</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3231,33 +3871,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bibliotekvej 62</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2091211</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F65">
+      <c r="H65">
         <v>1472</v>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t xml:space="preserve">311622365</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3281,33 +3931,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bødkerporten 6B</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2159279</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F66">
+      <c r="H66">
         <v>1712</v>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t xml:space="preserve">311622355</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3331,33 +3991,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Avedøre Tværvej 135B</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2159316</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F67">
+      <c r="H67">
         <v>356</v>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t xml:space="preserve">311622352</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3381,33 +4051,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovrevej 446</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t xml:space="preserve">8785521</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="F68">
+      <c r="H68">
         <v>4389</v>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t xml:space="preserve">311622359</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3431,33 +4111,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovrevej 241</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2090160</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F69">
+      <c r="H69">
         <v>2533</v>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t xml:space="preserve">311623162</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-08-25</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3481,33 +4171,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Høvedstensvej 35</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2091192</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F70">
+      <c r="H70">
         <v>8026</v>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t xml:space="preserve">311653142</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-01-10</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3531,33 +4231,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plovheldvej 4A</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023800</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="F71">
+      <c r="H71">
         <v>1662</v>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t xml:space="preserve">311669678</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3581,33 +4291,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plovheldvej 4A</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023800</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
         </is>
       </c>
-      <c r="F72">
+      <c r="H72">
         <v>2375</v>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t xml:space="preserve">311669678</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3631,33 +4351,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plovheldvej 4A</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023800</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F73">
+      <c r="H73">
         <v>1847</v>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t xml:space="preserve">311669678</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3681,33 +4411,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plovheldvej 4A</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023800</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F74">
+      <c r="H74">
         <v>1226</v>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t xml:space="preserve">311669678</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3731,33 +4471,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plovheldvej 4A</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023800</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F75">
+      <c r="H75">
         <v>1301</v>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t xml:space="preserve">311669678</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3781,33 +4531,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plovheldvej 4A</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023800</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F76">
+      <c r="H76">
         <v>2569</v>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t xml:space="preserve">311669678</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3831,33 +4591,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plovheldvej 4A</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023800</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F77">
+      <c r="H77">
         <v>606</v>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t xml:space="preserve">311669678</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3881,33 +4651,43 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plovheldvej 4A</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023800</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F78">
+      <c r="H78">
         <v>323</v>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t xml:space="preserve">311669678</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3931,33 +4711,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sollentuna Alle 6</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2079345</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F79">
+      <c r="H79">
         <v>1324</v>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t xml:space="preserve">311669680</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3981,33 +4771,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sollentuna Alle 6</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2079345</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F80">
+      <c r="H80">
         <v>1320</v>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t xml:space="preserve">311669680</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4031,33 +4831,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sollentuna Alle 4</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2079345</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F81">
+      <c r="H81">
         <v>445</v>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t xml:space="preserve">311669680</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4081,33 +4891,43 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sollentuna Alle 4</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2079345</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="F82">
+      <c r="H82">
         <v>2387</v>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t xml:space="preserve">311669680</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4131,33 +4951,43 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sollentuna Alle 6</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2079345</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F83">
+      <c r="H83">
         <v>493</v>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t xml:space="preserve">311669680</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
+      <c r="K83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4181,33 +5011,43 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sollentuna Alle 6</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2079345</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F84">
+      <c r="H84">
         <v>787</v>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t xml:space="preserve">311669680</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
+      <c r="K84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4231,33 +5071,43 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sollentuna Alle 6</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2079345</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F85">
+      <c r="H85">
         <v>1324</v>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t xml:space="preserve">311669680</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
+      <c r="K85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4281,33 +5131,43 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sollentuna Alle 6</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2079345</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F86">
+      <c r="H86">
         <v>1018</v>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t xml:space="preserve">311669680</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
+      <c r="K86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4331,33 +5191,43 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Risbjergvej 20</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2090722</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F87">
+      <c r="H87">
         <v>3240</v>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t xml:space="preserve">311669679</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
+      <c r="K87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4381,33 +5251,43 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
+          <t xml:space="preserve">Risbjergvej 20</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2090722</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F88">
+      <c r="H88">
         <v>554</v>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t xml:space="preserve">311669679</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
+      <c r="K88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4431,33 +5311,43 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Risbjergvej 20</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2090722</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F89">
+      <c r="H89">
         <v>1528</v>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t xml:space="preserve">311669679</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
+      <c r="K89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4481,33 +5371,43 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
+          <t xml:space="preserve">Risbjergvej 20</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2090722</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F90">
+      <c r="H90">
         <v>2017</v>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t xml:space="preserve">311669679</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
+      <c r="K90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4531,33 +5431,43 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t xml:space="preserve">Risbjergvej 20</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2090722</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F91">
+      <c r="H91">
         <v>1008</v>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t xml:space="preserve">311669679</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
+      <c r="K91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4581,33 +5491,43 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
+          <t xml:space="preserve">Risbjergvej 20</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2090722</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F92">
+      <c r="H92">
         <v>664</v>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t xml:space="preserve">311669679</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
+      <c r="K92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4631,33 +5551,43 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
+          <t xml:space="preserve">Risbjergvej 20</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2090722</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F93">
+      <c r="H93">
         <v>900</v>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t xml:space="preserve">311669679</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
+      <c r="K93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4681,33 +5611,43 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovrevej 278</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
           <t xml:space="preserve">7165564</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F94">
+      <c r="H94">
         <v>1345</v>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t xml:space="preserve">311669671</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
+      <c r="K94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4731,33 +5671,43 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovrevej 278</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
           <t xml:space="preserve">7165564</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F95">
+      <c r="H95">
         <v>6142</v>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t xml:space="preserve">311669668</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
+      <c r="K95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4781,33 +5731,43 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovrevej 278</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
           <t xml:space="preserve">7165564</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F96">
+      <c r="H96">
         <v>3329</v>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t xml:space="preserve">311669668</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
+      <c r="K96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4831,33 +5791,43 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovrevej 446</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
           <t xml:space="preserve">8785521</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F97">
+      <c r="H97">
         <v>6161</v>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t xml:space="preserve">311669688</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
+      <c r="K97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4881,33 +5851,43 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
+          <t xml:space="preserve">M Bechs Alle 122B</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025107</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="F98">
+      <c r="H98">
         <v>2141</v>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t xml:space="preserve">311670133</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
+      <c r="K98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4931,33 +5911,43 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
+          <t xml:space="preserve">M Bechs Alle 122C</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025107</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F99">
+      <c r="H99">
         <v>263</v>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t xml:space="preserve">311670133</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
+      <c r="K99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4981,33 +5971,43 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
+          <t xml:space="preserve">M Bechs Alle 122</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025107</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F100">
+      <c r="H100">
         <v>1272</v>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t xml:space="preserve">311670133</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
+      <c r="K100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5031,33 +6031,43 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
+          <t xml:space="preserve">M Bechs Alle 122</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025107</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F101">
+      <c r="H101">
         <v>4563</v>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t xml:space="preserve">311670133</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
+      <c r="K101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5081,33 +6091,43 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
+          <t xml:space="preserve">Frydenhøjstien 4</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2159169</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F102">
+      <c r="H102">
         <v>5857</v>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="I102" t="inlineStr">
         <is>
           <t xml:space="preserve">311670404</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
+      <c r="K102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5131,33 +6151,43 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
+          <t xml:space="preserve">Frydenhøjstien 2</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2159169</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F103">
+      <c r="H103">
         <v>969</v>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="I103" t="inlineStr">
         <is>
           <t xml:space="preserve">311670404</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
+      <c r="K103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5181,33 +6211,43 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
+          <t xml:space="preserve">Frydenhøjstien 8</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2159169</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F104">
+      <c r="H104">
         <v>537</v>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="I104" t="inlineStr">
         <is>
           <t xml:space="preserve">311670404</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
+      <c r="K104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5231,33 +6271,43 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
+          <t xml:space="preserve">Avedøre Tværvej 56</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
           <t xml:space="preserve">7029060</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F105">
+      <c r="H105">
         <v>363</v>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="I105" t="inlineStr">
         <is>
           <t xml:space="preserve">311670169</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
+      <c r="K105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5281,33 +6331,43 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
+          <t xml:space="preserve">Byvej 78</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
           <t xml:space="preserve">7029060</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F106">
+      <c r="H106">
         <v>398</v>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="I106" t="inlineStr">
         <is>
           <t xml:space="preserve">311670169</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
+      <c r="K106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5331,33 +6391,43 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
+          <t xml:space="preserve">Avedøre Havnevej 37</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
           <t xml:space="preserve">7706803</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F107">
+      <c r="H107">
         <v>1559</v>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="I107" t="inlineStr">
         <is>
           <t xml:space="preserve">311670403</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="J107" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
+      <c r="K107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5381,33 +6451,43 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
+          <t xml:space="preserve">Høvedstensvej 45</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2091204</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="G108" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F108">
+      <c r="H108">
         <v>1130</v>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311674024</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
+      <c r="I108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311674027</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
+      <c r="K108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5431,33 +6511,43 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
+          <t xml:space="preserve">Høvedstensvej 45B</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2091204</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F109">
+      <c r="H109">
         <v>1050</v>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311674024</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
+      <c r="I109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311674027</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
+      <c r="K109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5481,33 +6571,43 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
+          <t xml:space="preserve">Høvedstensvej 49</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2091204</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="G110" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F110">
+      <c r="H110">
         <v>865</v>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311674026</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
+      <c r="I110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311674027</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
+      <c r="K110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5531,33 +6631,43 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
+          <t xml:space="preserve">Høvedstensvej 45</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2091204</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
+      <c r="G111" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F111">
+      <c r="H111">
         <v>283</v>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311674024</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
+      <c r="I111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311674027</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
+      <c r="K111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5581,33 +6691,43 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
+          <t xml:space="preserve">Alarmpladsen 3</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
           <t xml:space="preserve">9494877</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="G112" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F112">
+      <c r="H112">
         <v>365</v>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="I112" t="inlineStr">
         <is>
           <t xml:space="preserve">311707954</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
+      <c r="J112" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-09-15</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
+      <c r="K112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5631,33 +6751,43 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovrevej 65</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023609</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="G113" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F113">
+      <c r="H113">
         <v>1289</v>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="I113" t="inlineStr">
         <is>
           <t xml:space="preserve">311716225</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
+      <c r="J113" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
+      <c r="K113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5681,33 +6811,43 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovre Enghavevej 17</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2077515</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="G114" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F114">
+      <c r="H114">
         <v>685</v>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="I114" t="inlineStr">
         <is>
           <t xml:space="preserve">311716223</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
+      <c r="J114" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
+      <c r="K114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5731,33 +6871,43 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovre Enghavevej 17</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2077515</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="G115" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F115">
+      <c r="H115">
         <v>685</v>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="I115" t="inlineStr">
         <is>
           <t xml:space="preserve">311716224</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
+      <c r="J115" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
+      <c r="K115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5781,33 +6931,43 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
+          <t xml:space="preserve">Svendebjergvej 2</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2079445</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="G116" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F116">
+      <c r="H116">
         <v>616</v>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="I116" t="inlineStr">
         <is>
           <t xml:space="preserve">311716226</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
+      <c r="J116" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
+      <c r="K116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5831,33 +6991,43 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
+          <t xml:space="preserve">Byvej 90B</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2157348</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="G117" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F117">
+      <c r="H117">
         <v>284</v>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="I117" t="inlineStr">
         <is>
           <t xml:space="preserve">311716216</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="J117" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
+      <c r="K117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5881,33 +7051,43 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
+          <t xml:space="preserve">Byvej 90</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2157348</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
+      <c r="G118" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F118">
+      <c r="H118">
         <v>680</v>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="I118" t="inlineStr">
         <is>
           <t xml:space="preserve">311716215</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
+      <c r="J118" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
+      <c r="K118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5931,33 +7111,43 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bødkerporten 2D</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2159279</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
+      <c r="G119" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F119">
+      <c r="H119">
         <v>351</v>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="I119" t="inlineStr">
         <is>
           <t xml:space="preserve">311716218</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
+      <c r="J119" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
+      <c r="K119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5981,33 +7171,43 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bødkerporten 4</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2159279</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
+      <c r="G120" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F120">
+      <c r="H120">
         <v>1201</v>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="I120" t="inlineStr">
         <is>
           <t xml:space="preserve">311716217</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
+      <c r="J120" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
+      <c r="K120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6031,33 +7231,43 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
+          <t xml:space="preserve">Byvej 248B</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2159956</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
+      <c r="G121" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F121">
+      <c r="H121">
         <v>608</v>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="I121" t="inlineStr">
         <is>
           <t xml:space="preserve">311716211</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
+      <c r="J121" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
+      <c r="K121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6081,33 +7291,43 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
+          <t xml:space="preserve">Byvej 248A</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2159956</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
+      <c r="G122" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F122">
+      <c r="H122">
         <v>619</v>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="I122" t="inlineStr">
         <is>
           <t xml:space="preserve">311716210</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
+      <c r="J122" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
+      <c r="K122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6131,33 +7351,43 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
+          <t xml:space="preserve">Byvej 248C</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2159956</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="G123" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F123">
+      <c r="H123">
         <v>619</v>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="I123" t="inlineStr">
         <is>
           <t xml:space="preserve">311716212</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
+      <c r="J123" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
+      <c r="K123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6181,33 +7411,43 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vedbyholm 8</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2160430</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="G124" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F124">
+      <c r="H124">
         <v>589</v>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="I124" t="inlineStr">
         <is>
           <t xml:space="preserve">311716227</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
+      <c r="J124" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
+      <c r="K124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6231,33 +7471,43 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
+          <t xml:space="preserve">Alarmpladsen 6A</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
           <t xml:space="preserve">8490054</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="G125" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
         </is>
       </c>
-      <c r="F125">
+      <c r="H125">
         <v>366</v>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="I125" t="inlineStr">
         <is>
           <t xml:space="preserve">311716208</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
+      <c r="J125" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
+      <c r="K125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6281,33 +7531,43 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vestre Kvartergade 5</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
           <t xml:space="preserve">9889329</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
+      <c r="G126" t="inlineStr">
         <is>
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c r="F126">
+      <c r="H126">
         <v>335</v>
       </c>
-      <c r="G126" t="inlineStr">
+      <c r="I126" t="inlineStr">
         <is>
           <t xml:space="preserve">311716228</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
+      <c r="J126" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
+      <c r="K126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6331,33 +7591,43 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vestre Kvartergade 20</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
           <t xml:space="preserve">9889332</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="G127" t="inlineStr">
         <is>
           <t xml:space="preserve">25</t>
         </is>
       </c>
-      <c r="F127">
+      <c r="H127">
         <v>423</v>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="I127" t="inlineStr">
         <is>
           <t xml:space="preserve">311716230</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
+      <c r="J127" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
+      <c r="K127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6381,33 +7651,43 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vestre Kvartergade 22</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
           <t xml:space="preserve">9889334</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="G128" t="inlineStr">
         <is>
           <t xml:space="preserve">24</t>
         </is>
       </c>
-      <c r="F128">
+      <c r="H128">
         <v>423</v>
       </c>
-      <c r="G128" t="inlineStr">
+      <c r="I128" t="inlineStr">
         <is>
           <t xml:space="preserve">311716229</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
+      <c r="J128" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
+      <c r="K128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6431,33 +7711,43 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fægtesalsvej 11</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
           <t xml:space="preserve">9889335</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="G129" t="inlineStr">
         <is>
           <t xml:space="preserve">59</t>
         </is>
       </c>
-      <c r="F129">
+      <c r="H129">
         <v>687</v>
       </c>
-      <c r="G129" t="inlineStr">
+      <c r="I129" t="inlineStr">
         <is>
           <t xml:space="preserve">311716220</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
+      <c r="J129" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
+      <c r="K129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6481,33 +7771,43 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fægtesalsvej 5</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
           <t xml:space="preserve">9889336</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="G130" t="inlineStr">
         <is>
           <t xml:space="preserve">31</t>
         </is>
       </c>
-      <c r="F130">
+      <c r="H130">
         <v>1253</v>
       </c>
-      <c r="G130" t="inlineStr">
+      <c r="I130" t="inlineStr">
         <is>
           <t xml:space="preserve">311716222</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
+      <c r="J130" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
+      <c r="K130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6531,33 +7831,43 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedporten 6</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
           <t xml:space="preserve">8490055</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="G131" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F131">
+      <c r="H131">
         <v>736</v>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="I131" t="inlineStr">
         <is>
           <t xml:space="preserve">311723773</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
+      <c r="J131" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-11-21</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
+      <c r="K131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6581,33 +7891,43 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
+          <t xml:space="preserve">Idrætsvej 75</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2079621</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="G132" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F132">
+      <c r="H132">
         <v>916</v>
       </c>
-      <c r="G132" t="inlineStr">
+      <c r="I132" t="inlineStr">
         <is>
           <t xml:space="preserve">311726046</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
+      <c r="J132" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-11-30</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
+      <c r="K132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6631,33 +7951,43 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bibliotekvej 52A</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
           <t xml:space="preserve">100191021</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
+      <c r="G133" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F133">
+      <c r="H133">
         <v>569</v>
       </c>
-      <c r="G133" t="inlineStr">
+      <c r="I133" t="inlineStr">
         <is>
           <t xml:space="preserve">311740622</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
+      <c r="J133" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-02-22</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
+      <c r="K133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6681,33 +8011,43 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
+          <t xml:space="preserve">Byvej 56</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2157286</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
+      <c r="G134" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F134">
+      <c r="H134">
         <v>563</v>
       </c>
-      <c r="G134" t="inlineStr">
+      <c r="I134" t="inlineStr">
         <is>
           <t xml:space="preserve">311740693</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
+      <c r="J134" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-02-23</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
+      <c r="K134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6731,33 +8071,43 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
+          <t xml:space="preserve">Svejbækvej 5</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8600</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
           <t xml:space="preserve">1461683</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
+      <c r="G135" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F135">
+      <c r="H135">
         <v>863</v>
       </c>
-      <c r="G135" t="inlineStr">
+      <c r="I135" t="inlineStr">
         <is>
           <t xml:space="preserve">311814921</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
+      <c r="J135" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
+      <c r="K135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6781,33 +8131,43 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bytoften 29</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025808</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
+      <c r="G136" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F136">
+      <c r="H136">
         <v>781</v>
       </c>
-      <c r="G136" t="inlineStr">
+      <c r="I136" t="inlineStr">
         <is>
           <t xml:space="preserve">311814922</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
+      <c r="J136" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
+      <c r="K136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6831,33 +8191,43 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bytoften 29</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025808</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
+      <c r="G137" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F137">
+      <c r="H137">
         <v>856</v>
       </c>
-      <c r="G137" t="inlineStr">
+      <c r="I137" t="inlineStr">
         <is>
           <t xml:space="preserve">311814922</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
+      <c r="J137" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
+      <c r="K137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6881,33 +8251,43 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovregade 59</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025855</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
+      <c r="G138" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F138">
+      <c r="H138">
         <v>361</v>
       </c>
-      <c r="G138" t="inlineStr">
+      <c r="I138" t="inlineStr">
         <is>
           <t xml:space="preserve">311814917</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
+      <c r="J138" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
+      <c r="K138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6931,33 +8311,43 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gammel Køge Landevej 276</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
           <t xml:space="preserve">7028595</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="G139" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F139">
+      <c r="H139">
         <v>416</v>
       </c>
-      <c r="G139" t="inlineStr">
+      <c r="I139" t="inlineStr">
         <is>
           <t xml:space="preserve">311814918</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
+      <c r="J139" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
+      <c r="K139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6981,33 +8371,43 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
           <t xml:space="preserve">7028726</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
+      <c r="G140" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F140">
+      <c r="H140">
         <v>430</v>
       </c>
-      <c r="G140" t="inlineStr">
+      <c r="I140" t="inlineStr">
         <is>
           <t xml:space="preserve">311814920</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
+      <c r="J140" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
+      <c r="K140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7031,33 +8431,43 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
+          <t xml:space="preserve">Næsborgvej 90</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
           <t xml:space="preserve">7028766</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="G141" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F141">
+      <c r="H141">
         <v>458</v>
       </c>
-      <c r="G141" t="inlineStr">
+      <c r="I141" t="inlineStr">
         <is>
           <t xml:space="preserve">311814924</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
+      <c r="J141" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
+      <c r="K141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7081,33 +8491,43 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovregade 49</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
           <t xml:space="preserve">8101016</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
+      <c r="G142" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F142">
+      <c r="H142">
         <v>938</v>
       </c>
-      <c r="G142" t="inlineStr">
+      <c r="I142" t="inlineStr">
         <is>
           <t xml:space="preserve">311814900</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
+      <c r="J142" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
+      <c r="K142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7131,33 +8551,43 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østre Messegade 6</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
           <t xml:space="preserve">9597370</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
+      <c r="G143" t="inlineStr">
         <is>
           <t xml:space="preserve">70</t>
         </is>
       </c>
-      <c r="F143">
+      <c r="H143">
         <v>633</v>
       </c>
-      <c r="G143" t="inlineStr">
+      <c r="I143" t="inlineStr">
         <is>
           <t xml:space="preserve">311814928</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
+      <c r="J143" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
+      <c r="K143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7181,33 +8611,43 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ejby Alle 34</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
           <t xml:space="preserve">9807242</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
+      <c r="G144" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F144">
+      <c r="H144">
         <v>1483</v>
       </c>
-      <c r="G144" t="inlineStr">
+      <c r="I144" t="inlineStr">
         <is>
           <t xml:space="preserve">311814923</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
+      <c r="J144" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
+      <c r="K144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7231,33 +8671,43 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
+          <t xml:space="preserve">Søren Jeppesens Vej 3</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8420</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
           <t xml:space="preserve">4166473</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
+      <c r="G145" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F145">
+      <c r="H145">
         <v>1058</v>
       </c>
-      <c r="G145" t="inlineStr">
+      <c r="I145" t="inlineStr">
         <is>
           <t xml:space="preserve">311816487</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
+      <c r="J145" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-03-10</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
+      <c r="K145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7281,33 +8731,43 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
+          <t xml:space="preserve">Immerkær 38</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
           <t xml:space="preserve">1300623</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
+      <c r="G146" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F146">
+      <c r="H146">
         <v>660</v>
       </c>
-      <c r="G146" t="inlineStr">
+      <c r="I146" t="inlineStr">
         <is>
           <t xml:space="preserve">311821770</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
+      <c r="J146" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
+      <c r="K146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7331,33 +8791,43 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovrevej 98</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023815</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
+      <c r="G147" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F147">
+      <c r="H147">
         <v>320</v>
       </c>
-      <c r="G147" t="inlineStr">
+      <c r="I147" t="inlineStr">
         <is>
           <t xml:space="preserve">311821767</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
+      <c r="J147" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
+      <c r="K147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7381,33 +8851,43 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
+          <t xml:space="preserve">Femagervej 37</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024782</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
+      <c r="G148" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F148">
+      <c r="H148">
         <v>276</v>
       </c>
-      <c r="G148" t="inlineStr">
+      <c r="I148" t="inlineStr">
         <is>
           <t xml:space="preserve">311821760</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
+      <c r="J148" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
+      <c r="K148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7431,33 +8911,43 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovrevej 138</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025821</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
+      <c r="G149" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F149">
+      <c r="H149">
         <v>384</v>
       </c>
-      <c r="G149" t="inlineStr">
+      <c r="I149" t="inlineStr">
         <is>
           <t xml:space="preserve">311821758</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
+      <c r="J149" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
+      <c r="K149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7481,33 +8971,43 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovre Enghavevej 21</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2081592</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
+      <c r="G150" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F150">
+      <c r="H150">
         <v>303</v>
       </c>
-      <c r="G150" t="inlineStr">
+      <c r="I150" t="inlineStr">
         <is>
           <t xml:space="preserve">311821754</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
+      <c r="J150" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
+      <c r="K150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7531,33 +9031,43 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovrevej 280</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
           <t xml:space="preserve">7165564</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
+      <c r="G151" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F151">
+      <c r="H151">
         <v>6412</v>
       </c>
-      <c r="G151" t="inlineStr">
+      <c r="I151" t="inlineStr">
         <is>
           <t xml:space="preserve">311821755</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
+      <c r="J151" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
+      <c r="K151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7581,33 +9091,43 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lille Friheden 1</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
           <t xml:space="preserve">9590756</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
+      <c r="G152" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F152">
+      <c r="H152">
         <v>498</v>
       </c>
-      <c r="G152" t="inlineStr">
+      <c r="I152" t="inlineStr">
         <is>
           <t xml:space="preserve">311821766</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
+      <c r="J152" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
+      <c r="K152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7631,33 +9151,43 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østre Messegade 5</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
           <t xml:space="preserve">9889326</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
+      <c r="G153" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F153">
+      <c r="H153">
         <v>445</v>
       </c>
-      <c r="G153" t="inlineStr">
+      <c r="I153" t="inlineStr">
         <is>
           <t xml:space="preserve">311821765</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
+      <c r="J153" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
+      <c r="K153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7681,33 +9211,43 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
+          <t xml:space="preserve">Alarmpladsen 2</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
           <t xml:space="preserve">9889328</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
+      <c r="G154" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F154">
+      <c r="H154">
         <v>925</v>
       </c>
-      <c r="G154" t="inlineStr">
+      <c r="I154" t="inlineStr">
         <is>
           <t xml:space="preserve">311821763</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
+      <c r="J154" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
+      <c r="K154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7731,33 +9271,43 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
+          <t xml:space="preserve">Præstemosen 209</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025114</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
+      <c r="G155" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F155">
+      <c r="H155">
         <v>319</v>
       </c>
-      <c r="G155" t="inlineStr">
+      <c r="I155" t="inlineStr">
         <is>
           <t xml:space="preserve">311897780</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
+      <c r="J155" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-04-29</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
+      <c r="K155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7781,33 +9331,43 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
+          <t xml:space="preserve">Præstemosen 209</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025114</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
+      <c r="G156" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F156">
+      <c r="H156">
         <v>1189</v>
       </c>
-      <c r="G156" t="inlineStr">
+      <c r="I156" t="inlineStr">
         <is>
           <t xml:space="preserve">311897779</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
+      <c r="J156" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-04-29</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
+      <c r="K156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7831,33 +9391,43 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egevolden 106</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2160102</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
+      <c r="G157" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F157">
+      <c r="H157">
         <v>4371</v>
       </c>
-      <c r="G157" t="inlineStr">
+      <c r="I157" t="inlineStr">
         <is>
           <t xml:space="preserve">311897781</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
+      <c r="J157" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-04-29</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
+      <c r="K157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7881,33 +9451,43 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egevolden 106</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2160102</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
+      <c r="G158" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F158">
+      <c r="H158">
         <v>2187</v>
       </c>
-      <c r="G158" t="inlineStr">
+      <c r="I158" t="inlineStr">
         <is>
           <t xml:space="preserve">311897781</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
+      <c r="J158" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-04-29</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
+      <c r="K158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7931,33 +9511,43 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egevolden 106</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2160102</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
+      <c r="G159" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F159">
+      <c r="H159">
         <v>3349</v>
       </c>
-      <c r="G159" t="inlineStr">
+      <c r="I159" t="inlineStr">
         <is>
           <t xml:space="preserve">311897781</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
+      <c r="J159" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-04-29</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
+      <c r="K159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7981,33 +9571,43 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egevolden 106</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2160102</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
+      <c r="G160" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F160">
+      <c r="H160">
         <v>362</v>
       </c>
-      <c r="G160" t="inlineStr">
+      <c r="I160" t="inlineStr">
         <is>
           <t xml:space="preserve">311897781</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
+      <c r="J160" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-04-29</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
+      <c r="K160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8031,33 +9631,43 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egevolden 100</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2160102</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
+      <c r="G161" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F161">
+      <c r="H161">
         <v>468</v>
       </c>
-      <c r="G161" t="inlineStr">
+      <c r="I161" t="inlineStr">
         <is>
           <t xml:space="preserve">311897781</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
+      <c r="J161" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-04-29</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
+      <c r="K161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8081,33 +9691,43 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
+          <t xml:space="preserve">Strandhavevej 7</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2081511</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
+      <c r="G162" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F162">
+      <c r="H162">
         <v>721</v>
       </c>
-      <c r="G162" t="inlineStr">
+      <c r="I162" t="inlineStr">
         <is>
           <t xml:space="preserve">311903567</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
+      <c r="J162" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
+      <c r="K162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8131,33 +9751,43 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
+          <t xml:space="preserve">Høvedstensvej 19</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2091170</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
+      <c r="G163" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F163">
+      <c r="H163">
         <v>1000</v>
       </c>
-      <c r="G163" t="inlineStr">
+      <c r="I163" t="inlineStr">
         <is>
           <t xml:space="preserve">311903573</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
+      <c r="J163" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
+      <c r="K163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8181,33 +9811,43 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
+          <t xml:space="preserve">Høvedstensvej 21</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2091170</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
+      <c r="G164" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F164">
+      <c r="H164">
         <v>1611</v>
       </c>
-      <c r="G164" t="inlineStr">
+      <c r="I164" t="inlineStr">
         <is>
           <t xml:space="preserve">311903573</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
+      <c r="J164" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
+      <c r="K164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8231,33 +9871,43 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
+          <t xml:space="preserve">Høvedstensvej 19</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
           <t xml:space="preserve">2091170</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
+      <c r="G165" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F165">
+      <c r="H165">
         <v>580</v>
       </c>
-      <c r="G165" t="inlineStr">
+      <c r="I165" t="inlineStr">
         <is>
           <t xml:space="preserve">311903573</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
+      <c r="J165" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
+      <c r="K165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8281,33 +9931,43 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
+          <t xml:space="preserve">Høvedstensvej 21</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
           <t xml:space="preserve">2091170</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
+      <c r="G166" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F166">
+      <c r="H166">
         <v>1223</v>
       </c>
-      <c r="G166" t="inlineStr">
+      <c r="I166" t="inlineStr">
         <is>
           <t xml:space="preserve">311903573</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
+      <c r="J166" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
+      <c r="K166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8331,33 +9991,43 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovre Enghavevej 6</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
           <t xml:space="preserve">7028726</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
+      <c r="G167" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F167">
+      <c r="H167">
         <v>324</v>
       </c>
-      <c r="G167" t="inlineStr">
+      <c r="I167" t="inlineStr">
         <is>
           <t xml:space="preserve">311903569</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
+      <c r="J167" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
+      <c r="K167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8381,33 +10051,43 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kettegård Alle 2</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
           <t xml:space="preserve">7028740</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
+      <c r="G168" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F168">
+      <c r="H168">
         <v>1703</v>
       </c>
-      <c r="G168" t="inlineStr">
+      <c r="I168" t="inlineStr">
         <is>
           <t xml:space="preserve">311903570</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
+      <c r="J168" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
+      <c r="K168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8431,33 +10111,43 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kettegård Alle 4</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
           <t xml:space="preserve">7028740</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr">
+      <c r="G169" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="F169">
+      <c r="H169">
         <v>345</v>
       </c>
-      <c r="G169" t="inlineStr">
+      <c r="I169" t="inlineStr">
         <is>
           <t xml:space="preserve">311903570</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
+      <c r="J169" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
+      <c r="K169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8481,33 +10171,43 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvidovrevej 218</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
           <t xml:space="preserve">7028740</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
+      <c r="G170" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F170">
+      <c r="H170">
         <v>1337</v>
       </c>
-      <c r="G170" t="inlineStr">
+      <c r="I170" t="inlineStr">
         <is>
           <t xml:space="preserve">311903570</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
+      <c r="J170" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
+      <c r="K170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8531,33 +10231,43 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kettegård Alle 2</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
           <t xml:space="preserve">7028740</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
+      <c r="G171" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F171">
+      <c r="H171">
         <v>663</v>
       </c>
-      <c r="G171" t="inlineStr">
+      <c r="I171" t="inlineStr">
         <is>
           <t xml:space="preserve">311903570</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
+      <c r="J171" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
+      <c r="K171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8581,33 +10291,43 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kettegård Alle 2</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
           <t xml:space="preserve">7028740</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr">
+      <c r="G172" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F172">
+      <c r="H172">
         <v>273</v>
       </c>
-      <c r="G172" t="inlineStr">
+      <c r="I172" t="inlineStr">
         <is>
           <t xml:space="preserve">311903570</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
+      <c r="J172" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
+      <c r="K172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8631,33 +10351,43 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kettegård Alle 2</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
           <t xml:space="preserve">7028740</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
+      <c r="G173" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F173">
+      <c r="H173">
         <v>1925</v>
       </c>
-      <c r="G173" t="inlineStr">
+      <c r="I173" t="inlineStr">
         <is>
           <t xml:space="preserve">311903570</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
+      <c r="J173" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
+      <c r="K173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8681,39 +10411,49 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kettegård Alle 4</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
           <t xml:space="preserve">7028740</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
+      <c r="G174" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F174">
+      <c r="H174">
         <v>1256</v>
       </c>
-      <c r="G174" t="inlineStr">
+      <c r="I174" t="inlineStr">
         <is>
           <t xml:space="preserve">311903570</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
+      <c r="J174" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
+      <c r="K174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J174"/>
+  <autoFilter ref="A1:L174"/>
 </worksheet>
 </file>
--- a/public/exports/55606617.xlsx
+++ b/public/exports/55606617.xlsx
@@ -91,7 +91,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 72</t>
+          <t xml:space="preserve">Avedøre Slettevej 7C</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -101,16 +101,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100822249</t>
+          <t xml:space="preserve">8963405</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H2">
-        <v>1058</v>
+        <v>1989</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -226,11 +226,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H4">
-        <v>427</v>
+        <v>1058</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,7 +271,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Catherine Boothsvej 20</t>
+          <t xml:space="preserve">Byvej 72</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -281,16 +281,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">100854515</t>
+          <t xml:space="preserve">100822249</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="H5">
-        <v>1283</v>
+        <v>427</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,7 +331,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 65A</t>
+          <t xml:space="preserve">Catherine Boothsvej 20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -341,7 +341,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079625</t>
+          <t xml:space="preserve">100854515</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -350,7 +350,7 @@
         </is>
       </c>
       <c r="H6">
-        <v>342</v>
+        <v>1283</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,7 +391,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 45C</t>
+          <t xml:space="preserve">Hvidovrevej 361A</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -401,16 +401,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091223</t>
+          <t xml:space="preserve">7028726</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H7">
-        <v>721</v>
+        <v>546</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,7 +451,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karise Alle 29</t>
+          <t xml:space="preserve">Hvidovrevej 361C</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -461,16 +461,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">226182</t>
+          <t xml:space="preserve">7028726</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H8">
-        <v>1836</v>
+        <v>546</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karise Alle 31</t>
+          <t xml:space="preserve">Høvedstensvej 45C</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -521,16 +521,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">226183</t>
+          <t xml:space="preserve">2091223</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H9">
-        <v>3484</v>
+        <v>721</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krogstens Alle 51</t>
+          <t xml:space="preserve">Idrætsvej 65A</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -581,16 +581,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">226183</t>
+          <t xml:space="preserve">2079625</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H10">
-        <v>3648</v>
+        <v>342</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 432</t>
+          <t xml:space="preserve">Strandhavevej 218</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -641,16 +641,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">228394, 228395, 228397, 228398, 228399, 228396</t>
+          <t xml:space="preserve">713681, 2080863</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H11">
-        <v>3996</v>
+        <v>581</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tavlekærsvej 166</t>
+          <t xml:space="preserve">Strandhavevej 59</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -701,16 +701,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">228812</t>
+          <t xml:space="preserve">713690, 2080863</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H12">
-        <v>1671</v>
+        <v>382</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tavlekærsvej 164</t>
+          <t xml:space="preserve">Hvidovregade 41A</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">228813</t>
+          <t xml:space="preserve">2024338</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -770,21 +770,21 @@
         </is>
       </c>
       <c r="H13">
-        <v>4660</v>
+        <v>650</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200056021</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-12-16</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 361A</t>
+          <t xml:space="preserve">Hvidovregade 41C</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -821,30 +821,30 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028726</t>
+          <t xml:space="preserve">2024338</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H14">
-        <v>546</v>
+        <v>650</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200056021</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-12-16</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 361C</t>
+          <t xml:space="preserve">Hvidovregade 41E</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -881,30 +881,30 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028726</t>
+          <t xml:space="preserve">2024338</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H15">
-        <v>546</v>
+        <v>650</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200056021</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-12-16</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandhavevej 218</t>
+          <t xml:space="preserve">Hvidovregade 41G</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -941,30 +941,30 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">713681, 2080863</t>
+          <t xml:space="preserve">2024338</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H16">
-        <v>581</v>
+        <v>650</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200056021</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-12-16</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandhavevej 59</t>
+          <t xml:space="preserve">Hvidovregade 41K</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1001,30 +1001,30 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">713690, 2080863</t>
+          <t xml:space="preserve">2024382</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H17">
-        <v>382</v>
+        <v>1522</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200056022</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-12-16</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avedøre Slettevej 7C</t>
+          <t xml:space="preserve">Hvidovrevej 446</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">8963405</t>
+          <t xml:space="preserve">8785521</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1070,21 +1070,21 @@
         </is>
       </c>
       <c r="H18">
-        <v>1989</v>
+        <v>4156</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200055994</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-12-16</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovregade 41A</t>
+          <t xml:space="preserve">Hvidovrevej 241</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024338</t>
+          <t xml:space="preserve">2090160</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1130,16 +1130,16 @@
         </is>
       </c>
       <c r="H19">
-        <v>650</v>
+        <v>354</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056021</t>
+          <t xml:space="preserve">311076836</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-16</t>
+          <t xml:space="preserve">2024-10-03</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovregade 41C</t>
+          <t xml:space="preserve">Hvidovre Strandvej 31H</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1181,35 +1181,35 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024338</t>
+          <t xml:space="preserve">713683, 2080863</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H20">
-        <v>650</v>
+        <v>308</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056021</t>
+          <t xml:space="preserve">311231684</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-16</t>
+          <t xml:space="preserve">2027-03-02</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovregade 41E</t>
+          <t xml:space="preserve">Hvidovrevej 432</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1241,35 +1241,35 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024338</t>
+          <t xml:space="preserve">228394, 228395, 228397, 228398, 228399, 228396</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H21">
-        <v>650</v>
+        <v>3996</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056021</t>
+          <t xml:space="preserve">311247295</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-16</t>
+          <t xml:space="preserve">2027-05-15</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovregade 41G</t>
+          <t xml:space="preserve">Byvej 248D</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1301,35 +1301,35 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024338</t>
+          <t xml:space="preserve">2159956</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H22">
-        <v>650</v>
+        <v>1497</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056021</t>
+          <t xml:space="preserve">311356616</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-16</t>
+          <t xml:space="preserve">2029-01-25</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovregade 41K</t>
+          <t xml:space="preserve">Catherine Boothsvej 22</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1361,35 +1361,35 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024382</t>
+          <t xml:space="preserve">2079383</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H23">
-        <v>1522</v>
+        <v>595</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056022</t>
+          <t xml:space="preserve">311567481</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-16</t>
+          <t xml:space="preserve">2031-12-13</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 446</t>
+          <t xml:space="preserve">Catherine Boothsvej 24A</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1421,35 +1421,35 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">8785521</t>
+          <t xml:space="preserve">2079383</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H24">
-        <v>4156</v>
+        <v>743</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055994</t>
+          <t xml:space="preserve">311567481</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-16</t>
+          <t xml:space="preserve">2031-12-13</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 241</t>
+          <t xml:space="preserve">Bødkerporten 1Y</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090160</t>
+          <t xml:space="preserve">2159266</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1490,26 +1490,26 @@
         </is>
       </c>
       <c r="H25">
-        <v>354</v>
+        <v>7598</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311076836</t>
+          <t xml:space="preserve">311586010</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-10-03</t>
+          <t xml:space="preserve">2031-12-15</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Strandvej 31H</t>
+          <t xml:space="preserve">Hvidovrevej 440</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1541,25 +1541,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">713683, 2080863</t>
+          <t xml:space="preserve">8785521</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H26">
-        <v>308</v>
+        <v>863</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311231684</t>
+          <t xml:space="preserve">311586012</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-02</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 248D</t>
+          <t xml:space="preserve">Hvidovrevej 440</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1601,25 +1601,25 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159956</t>
+          <t xml:space="preserve">8785521</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H27">
-        <v>1497</v>
+        <v>861</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311356616</t>
+          <t xml:space="preserve">311586012</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-25</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Catherine Boothsvej 22</t>
+          <t xml:space="preserve">Hvidovrevej 440</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1661,25 +1661,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079383</t>
+          <t xml:space="preserve">8785521</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H28">
-        <v>595</v>
+        <v>958</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311567481</t>
+          <t xml:space="preserve">311586012</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-13</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Catherine Boothsvej 24A</t>
+          <t xml:space="preserve">Hvidovrevej 440</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1721,25 +1721,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079383</t>
+          <t xml:space="preserve">8785521</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H29">
-        <v>743</v>
+        <v>858</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311567481</t>
+          <t xml:space="preserve">311586012</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-13</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bødkerporten 1Y</t>
+          <t xml:space="preserve">Hvidovrevej 440A</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1781,25 +1781,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159266</t>
+          <t xml:space="preserve">8785521</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H30">
-        <v>7598</v>
+        <v>6125</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586010</t>
+          <t xml:space="preserve">311586012</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-15</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 440A</t>
+          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1841,25 +1841,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">8785521</t>
+          <t xml:space="preserve">1301761</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H31">
-        <v>6125</v>
+        <v>894</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586012</t>
+          <t xml:space="preserve">311586014</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 440</t>
+          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1901,25 +1901,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">8785521</t>
+          <t xml:space="preserve">1301761</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H32">
-        <v>863</v>
+        <v>568</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586012</t>
+          <t xml:space="preserve">311586014</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 440</t>
+          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1961,25 +1961,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">8785521</t>
+          <t xml:space="preserve">1301761</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H33">
-        <v>861</v>
+        <v>493</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586012</t>
+          <t xml:space="preserve">311586014</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 440</t>
+          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2021,25 +2021,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">8785521</t>
+          <t xml:space="preserve">1301761</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H34">
-        <v>958</v>
+        <v>449</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586012</t>
+          <t xml:space="preserve">311586014</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 440</t>
+          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2081,25 +2081,25 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">8785521</t>
+          <t xml:space="preserve">1301761</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H35">
-        <v>858</v>
+        <v>445</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586012</t>
+          <t xml:space="preserve">311586014</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2146,11 +2146,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H36">
-        <v>894</v>
+        <v>798</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2206,11 +2206,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H37">
-        <v>568</v>
+        <v>798</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2266,11 +2266,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H38">
-        <v>493</v>
+        <v>772</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2326,11 +2326,11 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H39">
-        <v>449</v>
+        <v>884</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2386,11 +2386,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H40">
-        <v>445</v>
+        <v>621</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2446,11 +2446,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H41">
-        <v>798</v>
+        <v>621</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2506,11 +2506,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H42">
-        <v>798</v>
+        <v>621</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2566,11 +2566,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H43">
-        <v>772</v>
+        <v>1214</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
+          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2621,25 +2621,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301761</t>
+          <t xml:space="preserve">7028726</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H44">
-        <v>884</v>
+        <v>326</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586014</t>
+          <t xml:space="preserve">311588891</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-17</t>
+          <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
+          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2681,25 +2681,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301761</t>
+          <t xml:space="preserve">7028726</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H45">
-        <v>621</v>
+        <v>1167</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586014</t>
+          <t xml:space="preserve">311588891</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-17</t>
+          <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
+          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2741,25 +2741,25 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301761</t>
+          <t xml:space="preserve">7028726</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H46">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586014</t>
+          <t xml:space="preserve">311588891</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-17</t>
+          <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
+          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2801,25 +2801,25 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301761</t>
+          <t xml:space="preserve">7028726</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H47">
-        <v>621</v>
+        <v>785</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586014</t>
+          <t xml:space="preserve">311588891</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-17</t>
+          <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
+          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2861,25 +2861,25 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301761</t>
+          <t xml:space="preserve">7028726</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H48">
-        <v>1214</v>
+        <v>629</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586014</t>
+          <t xml:space="preserve">311588891</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-17</t>
+          <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2926,11 +2926,11 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H49">
-        <v>326</v>
+        <v>1151</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2986,11 +2986,11 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H50">
-        <v>1167</v>
+        <v>571</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
+          <t xml:space="preserve">Byvej 78</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3041,25 +3041,25 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028726</t>
+          <t xml:space="preserve">2157348</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H51">
-        <v>629</v>
+        <v>262</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588891</t>
+          <t xml:space="preserve">311590033</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-29</t>
+          <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
+          <t xml:space="preserve">Sollentuna Alle 1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3101,25 +3101,25 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028726</t>
+          <t xml:space="preserve">2079333</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H52">
-        <v>785</v>
+        <v>2799</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588891</t>
+          <t xml:space="preserve">311590065</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-29</t>
+          <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
+          <t xml:space="preserve">Sollentuna Alle 1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3161,25 +3161,25 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028726</t>
+          <t xml:space="preserve">2079333</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H53">
-        <v>629</v>
+        <v>1487</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588891</t>
+          <t xml:space="preserve">311590063</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-29</t>
+          <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
+          <t xml:space="preserve">Trædrejerporten 1A</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3221,25 +3221,25 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028726</t>
+          <t xml:space="preserve">2159280</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H54">
-        <v>1151</v>
+        <v>5757</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588891</t>
+          <t xml:space="preserve">311589965</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-29</t>
+          <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
+          <t xml:space="preserve">Sollentuna Alle 1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3281,25 +3281,25 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028726</t>
+          <t xml:space="preserve">2079333</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H55">
-        <v>571</v>
+        <v>904</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588891</t>
+          <t xml:space="preserve">311598300</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-29</t>
+          <t xml:space="preserve">2032-05-06</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3346,20 +3346,20 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H56">
-        <v>2799</v>
+        <v>839</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590065</t>
+          <t xml:space="preserve">311601624</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-01</t>
+          <t xml:space="preserve">2032-05-19</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3406,20 +3406,20 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H57">
-        <v>1487</v>
+        <v>863</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590063</t>
+          <t xml:space="preserve">311601624</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-01</t>
+          <t xml:space="preserve">2032-05-19</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 78</t>
+          <t xml:space="preserve">Avedøre Tværvej 135B</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2157348</t>
+          <t xml:space="preserve">2159316</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3470,16 +3470,16 @@
         </is>
       </c>
       <c r="H58">
-        <v>262</v>
+        <v>356</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590033</t>
+          <t xml:space="preserve">311622352</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-01</t>
+          <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trædrejerporten 1A</t>
+          <t xml:space="preserve">Bibliotekvej 62</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159280</t>
+          <t xml:space="preserve">2091211</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3530,16 +3530,16 @@
         </is>
       </c>
       <c r="H59">
-        <v>5757</v>
+        <v>1472</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311589965</t>
+          <t xml:space="preserve">311622365</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-01</t>
+          <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sollentuna Alle 1</t>
+          <t xml:space="preserve">Bødkerporten 6B</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079333</t>
+          <t xml:space="preserve">2159279</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3590,16 +3590,16 @@
         </is>
       </c>
       <c r="H60">
-        <v>904</v>
+        <v>1712</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598300</t>
+          <t xml:space="preserve">311622355</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-06</t>
+          <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sollentuna Alle 1</t>
+          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3641,25 +3641,25 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079333</t>
+          <t xml:space="preserve">1301761</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H61">
-        <v>839</v>
+        <v>402</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601624</t>
+          <t xml:space="preserve">311622362</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-19</t>
+          <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sollentuna Alle 1</t>
+          <t xml:space="preserve">Hvidovrevej 272</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3701,25 +3701,25 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079333</t>
+          <t xml:space="preserve">2091208</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H62">
-        <v>863</v>
+        <v>2623</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601624</t>
+          <t xml:space="preserve">311622363</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-19</t>
+          <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Strandvej 70A</t>
+          <t xml:space="preserve">Hvidovrevej 446</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301761</t>
+          <t xml:space="preserve">8785521</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3770,11 +3770,11 @@
         </is>
       </c>
       <c r="H63">
-        <v>402</v>
+        <v>4389</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622362</t>
+          <t xml:space="preserve">311622359</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 272</t>
+          <t xml:space="preserve">Hvidovrevej 241</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3821,25 +3821,25 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091208</t>
+          <t xml:space="preserve">2090160</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H64">
-        <v>2623</v>
+        <v>2533</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622363</t>
+          <t xml:space="preserve">311623162</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-23</t>
+          <t xml:space="preserve">2032-08-25</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bibliotekvej 62</t>
+          <t xml:space="preserve">Høvedstensvej 35</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091211</t>
+          <t xml:space="preserve">2091192</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3890,16 +3890,16 @@
         </is>
       </c>
       <c r="H65">
-        <v>1472</v>
+        <v>8026</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622365</t>
+          <t xml:space="preserve">311653142</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-23</t>
+          <t xml:space="preserve">2033-01-10</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bødkerporten 6B</t>
+          <t xml:space="preserve">Hvidovrevej 278</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159279</t>
+          <t xml:space="preserve">7165564</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3950,16 +3950,16 @@
         </is>
       </c>
       <c r="H66">
-        <v>1712</v>
+        <v>1345</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622355</t>
+          <t xml:space="preserve">311669671</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-23</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avedøre Tværvej 135B</t>
+          <t xml:space="preserve">Hvidovrevej 278</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4001,25 +4001,25 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159316</t>
+          <t xml:space="preserve">7165564</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H67">
-        <v>356</v>
+        <v>6142</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622352</t>
+          <t xml:space="preserve">311669668</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-23</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 446</t>
+          <t xml:space="preserve">Hvidovrevej 278</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4061,25 +4061,25 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">8785521</t>
+          <t xml:space="preserve">7165564</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H68">
-        <v>4389</v>
+        <v>3329</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622359</t>
+          <t xml:space="preserve">311669668</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-23</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 241</t>
+          <t xml:space="preserve">Hvidovrevej 446</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4121,25 +4121,25 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090160</t>
+          <t xml:space="preserve">8785521</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H69">
-        <v>2533</v>
+        <v>6161</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311623162</t>
+          <t xml:space="preserve">311669688</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-25</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 35</t>
+          <t xml:space="preserve">Karise Alle 29</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091192</t>
+          <t xml:space="preserve">226182</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4190,16 +4190,16 @@
         </is>
       </c>
       <c r="H70">
-        <v>8026</v>
+        <v>1836</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311653142</t>
+          <t xml:space="preserve">311669673</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-10</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plovheldvej 4A</t>
+          <t xml:space="preserve">Karise Alle 31</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4241,20 +4241,20 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023800</t>
+          <t xml:space="preserve">226183</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H71">
-        <v>1662</v>
+        <v>3484</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669678</t>
+          <t xml:space="preserve">311669673</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plovheldvej 4A</t>
+          <t xml:space="preserve">Krogstens Alle 51</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4301,20 +4301,20 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023800</t>
+          <t xml:space="preserve">226183</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H72">
-        <v>2375</v>
+        <v>3648</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669678</t>
+          <t xml:space="preserve">311669673</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4366,11 +4366,11 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H73">
-        <v>1847</v>
+        <v>1662</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -4426,11 +4426,11 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H74">
-        <v>1226</v>
+        <v>2375</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4486,11 +4486,11 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H75">
-        <v>1301</v>
+        <v>1847</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4546,11 +4546,11 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H76">
-        <v>2569</v>
+        <v>1226</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4606,11 +4606,11 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H77">
-        <v>606</v>
+        <v>1301</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4666,11 +4666,11 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H78">
-        <v>323</v>
+        <v>2569</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sollentuna Alle 6</t>
+          <t xml:space="preserve">Plovheldvej 4A</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4721,20 +4721,20 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079345</t>
+          <t xml:space="preserve">2023800</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H79">
-        <v>1324</v>
+        <v>606</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669680</t>
+          <t xml:space="preserve">311669678</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sollentuna Alle 6</t>
+          <t xml:space="preserve">Plovheldvej 4A</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4781,20 +4781,20 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079345</t>
+          <t xml:space="preserve">2023800</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H80">
-        <v>1320</v>
+        <v>323</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669680</t>
+          <t xml:space="preserve">311669678</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sollentuna Alle 4</t>
+          <t xml:space="preserve">Risbjergvej 20</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4841,20 +4841,20 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079345</t>
+          <t xml:space="preserve">2090722</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H81">
-        <v>445</v>
+        <v>3240</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669680</t>
+          <t xml:space="preserve">311669679</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sollentuna Alle 4</t>
+          <t xml:space="preserve">Risbjergvej 20</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4901,20 +4901,20 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079345</t>
+          <t xml:space="preserve">2090722</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H82">
-        <v>2387</v>
+        <v>554</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669680</t>
+          <t xml:space="preserve">311669679</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sollentuna Alle 6</t>
+          <t xml:space="preserve">Risbjergvej 20</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079345</t>
+          <t xml:space="preserve">2090722</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4970,11 +4970,11 @@
         </is>
       </c>
       <c r="H83">
-        <v>493</v>
+        <v>1528</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669680</t>
+          <t xml:space="preserve">311669679</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sollentuna Alle 6</t>
+          <t xml:space="preserve">Risbjergvej 20</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5021,20 +5021,20 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079345</t>
+          <t xml:space="preserve">2090722</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H84">
-        <v>787</v>
+        <v>2017</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669680</t>
+          <t xml:space="preserve">311669679</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sollentuna Alle 6</t>
+          <t xml:space="preserve">Risbjergvej 20</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5081,20 +5081,20 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079345</t>
+          <t xml:space="preserve">2090722</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H85">
-        <v>1324</v>
+        <v>1008</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669680</t>
+          <t xml:space="preserve">311669679</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sollentuna Alle 6</t>
+          <t xml:space="preserve">Risbjergvej 20</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5141,20 +5141,20 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079345</t>
+          <t xml:space="preserve">2090722</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H86">
-        <v>1018</v>
+        <v>664</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669680</t>
+          <t xml:space="preserve">311669679</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5206,11 +5206,11 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H87">
-        <v>3240</v>
+        <v>900</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Risbjergvej 20</t>
+          <t xml:space="preserve">Sollentuna Alle 4</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090722</t>
+          <t xml:space="preserve">2079345</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5270,11 +5270,11 @@
         </is>
       </c>
       <c r="H88">
-        <v>554</v>
+        <v>445</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669679</t>
+          <t xml:space="preserve">311669680</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Risbjergvej 20</t>
+          <t xml:space="preserve">Sollentuna Alle 4</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5321,20 +5321,20 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090722</t>
+          <t xml:space="preserve">2079345</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H89">
-        <v>1528</v>
+        <v>2387</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669679</t>
+          <t xml:space="preserve">311669680</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Risbjergvej 20</t>
+          <t xml:space="preserve">Sollentuna Alle 6</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5381,20 +5381,20 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090722</t>
+          <t xml:space="preserve">2079345</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H90">
-        <v>2017</v>
+        <v>1324</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669679</t>
+          <t xml:space="preserve">311669680</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Risbjergvej 20</t>
+          <t xml:space="preserve">Sollentuna Alle 6</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5441,20 +5441,20 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090722</t>
+          <t xml:space="preserve">2079345</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H91">
-        <v>1008</v>
+        <v>1320</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669679</t>
+          <t xml:space="preserve">311669680</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Risbjergvej 20</t>
+          <t xml:space="preserve">Sollentuna Alle 6</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5501,20 +5501,20 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090722</t>
+          <t xml:space="preserve">2079345</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H92">
-        <v>664</v>
+        <v>493</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669679</t>
+          <t xml:space="preserve">311669680</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Risbjergvej 20</t>
+          <t xml:space="preserve">Sollentuna Alle 6</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5561,20 +5561,20 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090722</t>
+          <t xml:space="preserve">2079345</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H93">
-        <v>900</v>
+        <v>787</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669679</t>
+          <t xml:space="preserve">311669680</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 278</t>
+          <t xml:space="preserve">Sollentuna Alle 6</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5621,20 +5621,20 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">7165564</t>
+          <t xml:space="preserve">2079345</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H94">
-        <v>1345</v>
+        <v>1324</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669671</t>
+          <t xml:space="preserve">311669680</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 278</t>
+          <t xml:space="preserve">Sollentuna Alle 6</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5681,20 +5681,20 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">7165564</t>
+          <t xml:space="preserve">2079345</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H95">
-        <v>6142</v>
+        <v>1018</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669668</t>
+          <t xml:space="preserve">311669680</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 278</t>
+          <t xml:space="preserve">Avedøre Havnevej 37</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5741,25 +5741,25 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">7165564</t>
+          <t xml:space="preserve">7706803</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H96">
-        <v>3329</v>
+        <v>1559</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669668</t>
+          <t xml:space="preserve">311670403</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-28</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 446</t>
+          <t xml:space="preserve">Avedøre Tværvej 56</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">8785521</t>
+          <t xml:space="preserve">7029060</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5810,16 +5810,16 @@
         </is>
       </c>
       <c r="H97">
-        <v>6161</v>
+        <v>363</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669688</t>
+          <t xml:space="preserve">311670169</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-28</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">M Bechs Alle 122B</t>
+          <t xml:space="preserve">Byvej 78</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5861,20 +5861,20 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025107</t>
+          <t xml:space="preserve">7029060</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H98">
-        <v>2141</v>
+        <v>398</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670133</t>
+          <t xml:space="preserve">311670169</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">M Bechs Alle 122C</t>
+          <t xml:space="preserve">Frydenhøjstien 2</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5921,20 +5921,20 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025107</t>
+          <t xml:space="preserve">2159169</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H99">
-        <v>263</v>
+        <v>969</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670133</t>
+          <t xml:space="preserve">311670404</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">M Bechs Alle 122</t>
+          <t xml:space="preserve">Frydenhøjstien 4</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -5981,20 +5981,20 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025107</t>
+          <t xml:space="preserve">2159169</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H100">
-        <v>1272</v>
+        <v>5857</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670133</t>
+          <t xml:space="preserve">311670404</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">M Bechs Alle 122</t>
+          <t xml:space="preserve">Frydenhøjstien 8</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6041,20 +6041,20 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025107</t>
+          <t xml:space="preserve">2159169</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H101">
-        <v>4563</v>
+        <v>537</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670133</t>
+          <t xml:space="preserve">311670404</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frydenhøjstien 4</t>
+          <t xml:space="preserve">M Bechs Alle 122</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6101,20 +6101,20 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159169</t>
+          <t xml:space="preserve">2025107</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H102">
-        <v>5857</v>
+        <v>1272</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670404</t>
+          <t xml:space="preserve">311670133</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frydenhøjstien 2</t>
+          <t xml:space="preserve">M Bechs Alle 122</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6161,20 +6161,20 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159169</t>
+          <t xml:space="preserve">2025107</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H103">
-        <v>969</v>
+        <v>4563</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670404</t>
+          <t xml:space="preserve">311670133</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frydenhøjstien 8</t>
+          <t xml:space="preserve">M Bechs Alle 122B</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6221,20 +6221,20 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159169</t>
+          <t xml:space="preserve">2025107</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H104">
-        <v>537</v>
+        <v>2141</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670404</t>
+          <t xml:space="preserve">311670133</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avedøre Tværvej 56</t>
+          <t xml:space="preserve">M Bechs Alle 122C</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6281,20 +6281,20 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">7029060</t>
+          <t xml:space="preserve">2025107</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H105">
-        <v>363</v>
+        <v>263</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670169</t>
+          <t xml:space="preserve">311670166</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 78</t>
+          <t xml:space="preserve">Tavlekærsvej 164</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6341,20 +6341,20 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">7029060</t>
+          <t xml:space="preserve">228813</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H106">
-        <v>398</v>
+        <v>4660</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670169</t>
+          <t xml:space="preserve">311670401</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avedøre Havnevej 37</t>
+          <t xml:space="preserve">Tavlekærsvej 166</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6401,20 +6401,20 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">7706803</t>
+          <t xml:space="preserve">228812</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H107">
-        <v>1559</v>
+        <v>1671</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670403</t>
+          <t xml:space="preserve">311670400</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674027</t>
+          <t xml:space="preserve">311674024</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 45B</t>
+          <t xml:space="preserve">Høvedstensvej 45</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6526,15 +6526,15 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H109">
-        <v>1050</v>
+        <v>283</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674027</t>
+          <t xml:space="preserve">311674024</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 49</t>
+          <t xml:space="preserve">Høvedstensvej 45B</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6586,15 +6586,15 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H110">
-        <v>865</v>
+        <v>1050</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674027</t>
+          <t xml:space="preserve">311674024</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 45</t>
+          <t xml:space="preserve">Høvedstensvej 49</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6646,15 +6646,15 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H111">
-        <v>283</v>
+        <v>865</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674027</t>
+          <t xml:space="preserve">311674026</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 65</t>
+          <t xml:space="preserve">Alarmpladsen 6A</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -6761,20 +6761,20 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023609</t>
+          <t xml:space="preserve">8490054</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H113">
-        <v>1289</v>
+        <v>366</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716225</t>
+          <t xml:space="preserve">311716208</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Enghavevej 17</t>
+          <t xml:space="preserve">Byvej 248A</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -6821,20 +6821,20 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2077515</t>
+          <t xml:space="preserve">2159956</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H114">
-        <v>685</v>
+        <v>619</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716223</t>
+          <t xml:space="preserve">311716210</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Enghavevej 17</t>
+          <t xml:space="preserve">Byvej 248B</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6881,20 +6881,20 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2077515</t>
+          <t xml:space="preserve">2159956</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H115">
-        <v>685</v>
+        <v>608</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716224</t>
+          <t xml:space="preserve">311716211</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svendebjergvej 2</t>
+          <t xml:space="preserve">Byvej 248C</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6941,20 +6941,20 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079445</t>
+          <t xml:space="preserve">2159956</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H116">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716226</t>
+          <t xml:space="preserve">311716212</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 90B</t>
+          <t xml:space="preserve">Byvej 90</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7006,15 +7006,15 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H117">
-        <v>284</v>
+        <v>680</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716216</t>
+          <t xml:space="preserve">311716215</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 90</t>
+          <t xml:space="preserve">Byvej 90B</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7066,15 +7066,15 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H118">
-        <v>680</v>
+        <v>284</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716215</t>
+          <t xml:space="preserve">311716216</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 248B</t>
+          <t xml:space="preserve">Fægtesalsvej 11</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7241,20 +7241,20 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159956</t>
+          <t xml:space="preserve">9889335</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">59</t>
         </is>
       </c>
       <c r="H121">
-        <v>608</v>
+        <v>687</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716211</t>
+          <t xml:space="preserve">311716220</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 248A</t>
+          <t xml:space="preserve">Fægtesalsvej 5</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7301,20 +7301,20 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159956</t>
+          <t xml:space="preserve">9889336</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="H122">
-        <v>619</v>
+        <v>1253</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716210</t>
+          <t xml:space="preserve">311716222</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 248C</t>
+          <t xml:space="preserve">Hvidovre Enghavevej 17</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7361,20 +7361,20 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159956</t>
+          <t xml:space="preserve">2077515</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H123">
-        <v>619</v>
+        <v>685</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716212</t>
+          <t xml:space="preserve">311716223</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vedbyholm 8</t>
+          <t xml:space="preserve">Hvidovre Enghavevej 17</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7421,20 +7421,20 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2160430</t>
+          <t xml:space="preserve">2077515</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H124">
-        <v>589</v>
+        <v>685</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716227</t>
+          <t xml:space="preserve">311716224</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -7471,7 +7471,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alarmpladsen 6A</t>
+          <t xml:space="preserve">Hvidovrevej 65</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7481,20 +7481,20 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">8490054</t>
+          <t xml:space="preserve">2023609</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H125">
-        <v>366</v>
+        <v>1289</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716208</t>
+          <t xml:space="preserve">311716225</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestre Kvartergade 5</t>
+          <t xml:space="preserve">Svendebjergvej 2</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -7541,20 +7541,20 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">9889329</t>
+          <t xml:space="preserve">2079445</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H126">
-        <v>335</v>
+        <v>616</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716228</t>
+          <t xml:space="preserve">311716226</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestre Kvartergade 20</t>
+          <t xml:space="preserve">Vedbyholm 8</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7601,20 +7601,20 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">9889332</t>
+          <t xml:space="preserve">2160430</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H127">
-        <v>423</v>
+        <v>589</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716230</t>
+          <t xml:space="preserve">311716227</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestre Kvartergade 22</t>
+          <t xml:space="preserve">Vestre Kvartergade 20</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">9889334</t>
+          <t xml:space="preserve">9889332</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="H128">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716229</t>
+          <t xml:space="preserve">311716230</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fægtesalsvej 11</t>
+          <t xml:space="preserve">Vestre Kvartergade 22</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -7721,20 +7721,20 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">9889335</t>
+          <t xml:space="preserve">9889334</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">59</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="H129">
-        <v>687</v>
+        <v>423</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716220</t>
+          <t xml:space="preserve">311716229</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fægtesalsvej 5</t>
+          <t xml:space="preserve">Vestre Kvartergade 5</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -7781,20 +7781,20 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">9889336</t>
+          <t xml:space="preserve">9889329</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="H130">
-        <v>1253</v>
+        <v>335</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716222</t>
+          <t xml:space="preserve">311716228</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -8066,22 +8066,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">740</t>
+          <t xml:space="preserve">167</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svejbækvej 5</t>
+          <t xml:space="preserve">Bytoften 29</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">8600</t>
+          <t xml:space="preserve">2650</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">1461683</t>
+          <t xml:space="preserve">2025808</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -8090,11 +8090,11 @@
         </is>
       </c>
       <c r="H135">
-        <v>863</v>
+        <v>781</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814921</t>
+          <t xml:space="preserve">311814922</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8146,11 +8146,11 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H136">
-        <v>781</v>
+        <v>856</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bytoften 29</t>
+          <t xml:space="preserve">Ejby Alle 34</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8201,20 +8201,20 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025808</t>
+          <t xml:space="preserve">9807242</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H137">
-        <v>856</v>
+        <v>1483</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814922</t>
+          <t xml:space="preserve">311814923</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovregade 59</t>
+          <t xml:space="preserve">Gammel Køge Landevej 276</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025855</t>
+          <t xml:space="preserve">7028595</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -8270,11 +8270,11 @@
         </is>
       </c>
       <c r="H138">
-        <v>361</v>
+        <v>416</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814917</t>
+          <t xml:space="preserve">311814918</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Køge Landevej 276</t>
+          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8321,20 +8321,20 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028595</t>
+          <t xml:space="preserve">7028726</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H139">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814918</t>
+          <t xml:space="preserve">311814920</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Enghavevej 2</t>
+          <t xml:space="preserve">Hvidovregade 49</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8381,20 +8381,20 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028726</t>
+          <t xml:space="preserve">8101016</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H140">
-        <v>430</v>
+        <v>938</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814920</t>
+          <t xml:space="preserve">311814900</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Næsborgvej 90</t>
+          <t xml:space="preserve">Hvidovregade 59</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -8441,20 +8441,20 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028766</t>
+          <t xml:space="preserve">2025855</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H141">
-        <v>458</v>
+        <v>361</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814924</t>
+          <t xml:space="preserve">311814917</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovregade 49</t>
+          <t xml:space="preserve">Næsborgvej 90</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -8501,20 +8501,20 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">8101016</t>
+          <t xml:space="preserve">7028766</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H142">
-        <v>938</v>
+        <v>458</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814900</t>
+          <t xml:space="preserve">311814924</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -8546,35 +8546,35 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">167</t>
+          <t xml:space="preserve">740</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Messegade 6</t>
+          <t xml:space="preserve">Svejbækvej 5</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2650</t>
+          <t xml:space="preserve">8600</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">9597370</t>
+          <t xml:space="preserve">1461683</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">70</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H143">
-        <v>633</v>
+        <v>863</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814928</t>
+          <t xml:space="preserve">311814921</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejby Alle 34</t>
+          <t xml:space="preserve">Østre Messegade 6</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -8621,20 +8621,20 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">9807242</t>
+          <t xml:space="preserve">9597370</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">70</t>
         </is>
       </c>
       <c r="H144">
-        <v>1483</v>
+        <v>633</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814923</t>
+          <t xml:space="preserve">311814928</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Immerkær 38</t>
+          <t xml:space="preserve">Alarmpladsen 2</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -8741,20 +8741,20 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300623</t>
+          <t xml:space="preserve">9889328</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H146">
-        <v>660</v>
+        <v>925</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821770</t>
+          <t xml:space="preserve">311821763</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 98</t>
+          <t xml:space="preserve">Femagervej 37</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023815</t>
+          <t xml:space="preserve">2024782</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -8810,11 +8810,11 @@
         </is>
       </c>
       <c r="H147">
-        <v>320</v>
+        <v>276</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821767</t>
+          <t xml:space="preserve">311821760</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Femagervej 37</t>
+          <t xml:space="preserve">Hvidovre Enghavevej 21</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024782</t>
+          <t xml:space="preserve">2081592</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -8870,11 +8870,11 @@
         </is>
       </c>
       <c r="H148">
-        <v>276</v>
+        <v>303</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821760</t>
+          <t xml:space="preserve">311821754</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Enghavevej 21</t>
+          <t xml:space="preserve">Hvidovrevej 280</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -8981,20 +8981,20 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2081592</t>
+          <t xml:space="preserve">7165564</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H150">
-        <v>303</v>
+        <v>6412</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821754</t>
+          <t xml:space="preserve">311821755</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 280</t>
+          <t xml:space="preserve">Hvidovrevej 98</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9041,20 +9041,20 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">7165564</t>
+          <t xml:space="preserve">2023815</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H151">
-        <v>6412</v>
+        <v>320</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821755</t>
+          <t xml:space="preserve">311821767</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lille Friheden 1</t>
+          <t xml:space="preserve">Immerkær 38</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9101,20 +9101,20 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">9590756</t>
+          <t xml:space="preserve">1300623</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H152">
-        <v>498</v>
+        <v>660</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821766</t>
+          <t xml:space="preserve">311821770</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Messegade 5</t>
+          <t xml:space="preserve">Lille Friheden 1</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9161,20 +9161,20 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">9889326</t>
+          <t xml:space="preserve">9590756</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H153">
-        <v>445</v>
+        <v>498</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821765</t>
+          <t xml:space="preserve">311821766</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alarmpladsen 2</t>
+          <t xml:space="preserve">Østre Messegade 5</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9221,20 +9221,20 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">9889328</t>
+          <t xml:space="preserve">9889326</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H154">
-        <v>925</v>
+        <v>445</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821763</t>
+          <t xml:space="preserve">311821765</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstemosen 209</t>
+          <t xml:space="preserve">Egevolden 100</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9281,20 +9281,20 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025114</t>
+          <t xml:space="preserve">2160102</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H155">
-        <v>319</v>
+        <v>468</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897780</t>
+          <t xml:space="preserve">311897781</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstemosen 209</t>
+          <t xml:space="preserve">Egevolden 106</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9341,20 +9341,20 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025114</t>
+          <t xml:space="preserve">2160102</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H156">
-        <v>1189</v>
+        <v>4371</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897779</t>
+          <t xml:space="preserve">311897781</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -9406,11 +9406,11 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H157">
-        <v>4371</v>
+        <v>2187</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -9466,11 +9466,11 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H158">
-        <v>2187</v>
+        <v>3349</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -9526,11 +9526,11 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H159">
-        <v>3349</v>
+        <v>362</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egevolden 106</t>
+          <t xml:space="preserve">Præstemosen 209</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -9581,20 +9581,20 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2160102</t>
+          <t xml:space="preserve">2025114</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H160">
-        <v>362</v>
+        <v>319</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897781</t>
+          <t xml:space="preserve">311897780</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egevolden 100</t>
+          <t xml:space="preserve">Præstemosen 209</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -9641,20 +9641,20 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2160102</t>
+          <t xml:space="preserve">2025114</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H161">
-        <v>468</v>
+        <v>1189</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897781</t>
+          <t xml:space="preserve">311897779</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandhavevej 7</t>
+          <t xml:space="preserve">Hvidovre Enghavevej 6</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -9701,20 +9701,20 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2081511</t>
+          <t xml:space="preserve">7028726</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H162">
-        <v>721</v>
+        <v>324</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903567</t>
+          <t xml:space="preserve">311903569</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -9751,7 +9751,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 19</t>
+          <t xml:space="preserve">Hvidovrevej 218</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -9761,20 +9761,20 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091170</t>
+          <t xml:space="preserve">7028740</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H163">
-        <v>1000</v>
+        <v>1337</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903573</t>
+          <t xml:space="preserve">311903570</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 21</t>
+          <t xml:space="preserve">Høvedstensvej 19</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -9826,11 +9826,11 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H164">
-        <v>1611</v>
+        <v>1000</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -9946,11 +9946,11 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H166">
-        <v>1223</v>
+        <v>1611</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -9991,7 +9991,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovre Enghavevej 6</t>
+          <t xml:space="preserve">Høvedstensvej 21</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10001,20 +10001,20 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028726</t>
+          <t xml:space="preserve">2091170</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H167">
-        <v>324</v>
+        <v>1223</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903569</t>
+          <t xml:space="preserve">311903573</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettegård Alle 4</t>
+          <t xml:space="preserve">Kettegård Alle 2</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10126,11 +10126,11 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H169">
-        <v>345</v>
+        <v>663</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 218</t>
+          <t xml:space="preserve">Kettegård Alle 2</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10186,11 +10186,11 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H170">
-        <v>1337</v>
+        <v>273</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
@@ -10246,11 +10246,11 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H171">
-        <v>663</v>
+        <v>1925</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettegård Alle 2</t>
+          <t xml:space="preserve">Kettegård Alle 4</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10306,11 +10306,11 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H172">
-        <v>273</v>
+        <v>345</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettegård Alle 2</t>
+          <t xml:space="preserve">Kettegård Alle 4</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10366,11 +10366,11 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H173">
-        <v>1925</v>
+        <v>1256</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettegård Alle 4</t>
+          <t xml:space="preserve">Strandhavevej 7</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -10421,20 +10421,20 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028740</t>
+          <t xml:space="preserve">2081511</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H174">
-        <v>1256</v>
+        <v>721</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903570</t>
+          <t xml:space="preserve">311903567</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">

--- a/public/exports/55606617.xlsx
+++ b/public/exports/55606617.xlsx
@@ -6294,7 +6294,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670166</t>
+          <t xml:space="preserve">311670133</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674024</t>
+          <t xml:space="preserve">311674028</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674024</t>
+          <t xml:space="preserve">311674028</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674024</t>
+          <t xml:space="preserve">311674028</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">

--- a/public/exports/55606617.xlsx
+++ b/public/exports/55606617.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L174"/>
+  <dimension ref="A1:M174"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -779,15 +839,20 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-12-16</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -839,15 +904,20 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-12-16</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -899,15 +969,20 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-12-16</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -959,15 +1034,20 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-12-16</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1019,15 +1099,20 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-12-16</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1079,15 +1164,20 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-12-16</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1139,15 +1229,20 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S (Glostrup)</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-10-03</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1199,15 +1294,20 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Center Øst</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-02</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1259,15 +1359,20 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-15</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1319,15 +1424,20 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-01-25</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1379,15 +1489,20 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-13</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1439,15 +1554,20 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-13</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1499,15 +1619,20 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-15</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1559,15 +1684,20 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1619,15 +1749,20 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1679,15 +1814,20 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1739,15 +1879,20 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1799,15 +1944,20 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1859,15 +2009,20 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1919,15 +2074,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1979,15 +2139,20 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2039,15 +2204,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2099,15 +2269,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2159,15 +2334,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2219,15 +2399,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2279,15 +2464,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2339,15 +2529,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2399,15 +2594,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-06</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-19</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-19</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-08-25</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-10</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5219,15 +5649,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5459,15 +5909,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6419,15 +6949,20 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6474,20 +7009,25 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674028</t>
+          <t xml:space="preserve">311674027</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6534,20 +7074,25 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674028</t>
+          <t xml:space="preserve">311674027</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6594,20 +7139,25 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674028</t>
+          <t xml:space="preserve">311674027</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6654,20 +7204,25 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674026</t>
+          <t xml:space="preserve">311674027</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6719,15 +7274,20 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-15</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6779,15 +7339,20 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7199,15 +7794,20 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7259,15 +7859,20 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7319,15 +7924,20 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7379,15 +7989,20 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7439,15 +8054,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7499,15 +8119,20 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7559,15 +8184,20 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7619,15 +8249,20 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7679,15 +8314,20 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7739,15 +8379,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7799,15 +8444,20 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-19</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7859,15 +8509,20 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-21</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7919,15 +8574,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-30</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7979,15 +8639,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-22</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8039,15 +8704,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-23</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8099,15 +8769,20 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8159,15 +8834,20 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8219,15 +8899,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8279,15 +8964,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8339,15 +9029,20 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8399,15 +9094,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8459,15 +9159,20 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8519,15 +9224,20 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8579,15 +9289,20 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8639,15 +9354,20 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8699,15 +9419,20 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-10</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8759,15 +9484,20 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8819,15 +9549,20 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8879,15 +9614,20 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8939,15 +9679,20 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8999,15 +9744,20 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9059,15 +9809,20 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9119,15 +9874,20 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9179,15 +9939,20 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9239,15 +10004,20 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9299,15 +10069,20 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-29</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9359,15 +10134,20 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-29</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9419,15 +10199,20 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-29</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9479,15 +10264,20 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-29</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9539,15 +10329,20 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-29</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9599,15 +10394,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-29</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9659,15 +10459,20 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-29</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9719,15 +10524,20 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9779,15 +10589,20 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9839,15 +10654,20 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9899,15 +10719,20 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9959,15 +10784,20 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10019,15 +10849,20 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10079,15 +10914,20 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10139,15 +10979,20 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10199,15 +11044,20 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10259,15 +11109,20 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10319,15 +11174,20 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10379,15 +11239,20 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10439,21 +11304,26 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L174" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L174"/>
+  <autoFilter ref="A1:M174"/>
 </worksheet>
 </file>
--- a/public/exports/55606617.xlsx
+++ b/public/exports/55606617.xlsx
@@ -7009,12 +7009,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674027</t>
+          <t xml:space="preserve">311674024</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674027</t>
+          <t xml:space="preserve">311674024</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674027</t>
+          <t xml:space="preserve">311674024</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -7204,12 +7204,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674027</t>
+          <t xml:space="preserve">311674026</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
